--- a/Metrics/Best_Models_Per_Company_Optimized.xlsx
+++ b/Metrics/Best_Models_Per_Company_Optimized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED416EE9-0B83-447D-91DC-3565CE4335C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB8DD09A-55A7-4930-B641-F9A21679959F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1601,7 +1601,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1647,12 +1646,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1957,9 +1957,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K499"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -2004,7 +2001,14 @@
         <v>4.4551520000000004E-3</v>
       </c>
       <c r="G2">
-        <v>-1.0284408221318799</v>
+        <v>-1.024401074526271</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="2">
+        <f>COUNTIF(B2:B510, "LSTM")</f>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -2027,14 +2031,14 @@
         <v>8.1764709999999994E-3</v>
       </c>
       <c r="G3">
-        <v>-1.269099703026753</v>
+        <v>-1.363739426379176</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" s="2">
-        <f>COUNTIF(B3:B511, "LSTM")</f>
-        <v>227</v>
+        <f>COUNTIF(B2:B510, "GRU")</f>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -2057,14 +2061,14 @@
         <v>5.2912483000000003E-2</v>
       </c>
       <c r="G4">
-        <v>-1.384917791451685</v>
+        <v>-1.5269879847936889</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2">
-        <f>COUNTIF(B3:B511, "GRU")</f>
-        <v>148</v>
+        <f>COUNTIF(B2:B510, "XGBoost")</f>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -2087,14 +2091,14 @@
         <v>4.1010680000000002E-3</v>
       </c>
       <c r="G5">
-        <v>-1.035090927606976</v>
+        <v>-1.05220032922639</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K5" s="2">
-        <f>COUNTIF(B3:B511, "XGBoost")</f>
-        <v>78</v>
+        <f>COUNTIF(B2:B510, "LightGBM")</f>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -2117,14 +2121,7 @@
         <v>3.6934569999999998E-3</v>
       </c>
       <c r="G6">
-        <v>-1.577784762735019</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K6" s="2">
-        <f>COUNTIF(B3:B511, "LightGBM")</f>
-        <v>44</v>
+        <v>-1.6660661151273961</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -2149,6 +2146,9 @@
       <c r="G7">
         <v>-0.99999999999720557</v>
       </c>
+      <c r="J7" s="3" t="s">
+        <v>509</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -2170,7 +2170,7 @@
         <v>2.9726100000000001E-3</v>
       </c>
       <c r="G8">
-        <v>-1.4274923922973859</v>
+        <v>-1.5014466130202311</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -2193,10 +2193,7 @@
         <v>8.5549000000000007E-3</v>
       </c>
       <c r="G9">
-        <v>-0.73086064064188094</v>
-      </c>
-      <c r="J9" t="s">
-        <v>509</v>
+        <v>-0.75076885630503165</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.35">
@@ -2216,7 +2213,7 @@
         <v>-0.111182188</v>
       </c>
       <c r="F10">
-        <v>150.24762509911201</v>
+        <v>1.50247625099112</v>
       </c>
       <c r="G10">
         <v>-1.0000000000000111</v>
@@ -2242,7 +2239,7 @@
         <v>0.270736843</v>
       </c>
       <c r="G11">
-        <v>-0.70002936105619118</v>
+        <v>-0.70384439994602743</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
@@ -2265,7 +2262,7 @@
         <v>3.9410695000000003E-2</v>
       </c>
       <c r="G12">
-        <v>-0.7999999999999996</v>
+        <v>-0.19999999999999829</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
@@ -2288,7 +2285,7 @@
         <v>1.5808811999999998E-2</v>
       </c>
       <c r="G13">
-        <v>-1.00143711249065</v>
+        <v>-1.053985082603845</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -2311,7 +2308,7 @@
         <v>4.1864600000000004E-3</v>
       </c>
       <c r="G14">
-        <v>-0.80585652554505283</v>
+        <v>-0.86436430472720893</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -2334,7 +2331,7 @@
         <v>4.0678823000000003E-2</v>
       </c>
       <c r="G15">
-        <v>-1.0000000000000031</v>
+        <v>-1.000000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
@@ -2357,7 +2354,7 @@
         <v>9.2291500000000002E-3</v>
       </c>
       <c r="G16">
-        <v>-1.146239170392944</v>
+        <v>-1.2407602185037201</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2377,10 +2374,10 @@
         <v>0.97456252600000004</v>
       </c>
       <c r="F17">
-        <v>1.3958407004054101</v>
+        <v>1.39584070040541E-2</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>-0.99999999999999933</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
@@ -2388,22 +2385,22 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C18">
-        <v>51684.144310000003</v>
+        <v>100207.8247</v>
       </c>
       <c r="D18">
-        <v>203.64666030000001</v>
+        <v>275.014678</v>
       </c>
       <c r="E18">
-        <v>0.36895307700000002</v>
+        <v>-0.22350559</v>
       </c>
       <c r="F18">
-        <v>1.6985612940000001</v>
+        <v>0.88484433699999998</v>
       </c>
       <c r="G18">
-        <v>-0.84094489430666208</v>
+        <v>-0.52769061096833003</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -2426,7 +2423,7 @@
         <v>4.3494750000000002E-3</v>
       </c>
       <c r="G19">
-        <v>-1.2069931478851501</v>
+        <v>-1.4113210690917479</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2446,7 +2443,7 @@
         <v>0.57196047900000002</v>
       </c>
       <c r="F20">
-        <v>7.0569574237992096</v>
+        <v>7.0569574237992094E-2</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -2472,7 +2469,7 @@
         <v>2.1511619999999999E-3</v>
       </c>
       <c r="G21">
-        <v>-1.1086996330480909</v>
+        <v>-1.190549053042431</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2503,22 +2500,22 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>0.25150879700000001</v>
+        <v>18.675118300000001</v>
       </c>
       <c r="D23">
-        <v>0.39388169899999997</v>
+        <v>3.5479479249999999</v>
       </c>
       <c r="E23">
-        <v>-11.72427661</v>
+        <v>0.85821004499999998</v>
       </c>
       <c r="F23">
-        <v>23.512763046345501</v>
+        <v>2.2082265E-2</v>
       </c>
       <c r="G23">
-        <v>-0.61039743091905507</v>
+        <v>-0.38223177778883022</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
@@ -2541,7 +2538,7 @@
         <v>1.6441159999999999E-3</v>
       </c>
       <c r="G24">
-        <v>-1.1547829779469061</v>
+        <v>-1.247516811850591</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -2564,7 +2561,7 @@
         <v>4.5508750000000002E-3</v>
       </c>
       <c r="G25">
-        <v>-1.1583779264735281</v>
+        <v>-1.2228696334978959</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -2610,7 +2607,7 @@
         <v>4.7336770000000004E-3</v>
       </c>
       <c r="G27">
-        <v>-1.4774899561884589</v>
+        <v>-1.473259130874091</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -2633,7 +2630,7 @@
         <v>5.2306002999999997E-2</v>
       </c>
       <c r="G28">
-        <v>-0.82156764342989808</v>
+        <v>-0.85793335521669623</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -2656,7 +2653,7 @@
         <v>0.16084226200000001</v>
       </c>
       <c r="G29">
-        <v>-1.0058541956100939</v>
+        <v>-1.065492585422203</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -2679,7 +2676,7 @@
         <v>5.2378484780000001</v>
       </c>
       <c r="G30">
-        <v>-0.71212505660658221</v>
+        <v>-0.16543830807449289</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -2699,10 +2696,10 @@
         <v>0.98634573199999998</v>
       </c>
       <c r="F31">
-        <v>0.41602801123467997</v>
+        <v>4.1602801123468E-3</v>
       </c>
       <c r="G31">
-        <v>-0.88639863275752118</v>
+        <v>-1.0434025482184</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
@@ -2745,7 +2742,7 @@
         <v>0.97570205600000004</v>
       </c>
       <c r="F33">
-        <v>3.7674437595840402</v>
+        <v>3.7674437595840403E-2</v>
       </c>
       <c r="G33">
         <v>-1</v>
@@ -2771,7 +2768,7 @@
         <v>3.1678696999999999E-2</v>
       </c>
       <c r="G34">
-        <v>-0.99999999999999944</v>
+        <v>-0.99999999999999778</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
@@ -2814,10 +2811,10 @@
         <v>0.97107469300000004</v>
       </c>
       <c r="F36">
-        <v>1.0400623898943999</v>
+        <v>1.0400623898944E-2</v>
       </c>
       <c r="G36">
-        <v>-1.000000000000002</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2840,7 +2837,7 @@
         <v>1.654193E-3</v>
       </c>
       <c r="G37">
-        <v>-1.3097041518318091</v>
+        <v>-1.4272585794927879</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2860,7 +2857,7 @@
         <v>-4.5311894419999996</v>
       </c>
       <c r="F38">
-        <v>81.646581096568397</v>
+        <v>0.81646581096568394</v>
       </c>
       <c r="G38">
         <v>-1</v>
@@ -2883,7 +2880,7 @@
         <v>-3.4669120389999999</v>
       </c>
       <c r="F39">
-        <v>37.904738701878003</v>
+        <v>0.37904738701877999</v>
       </c>
       <c r="G39">
         <v>-0.99999999999999956</v>
@@ -2909,7 +2906,7 @@
         <v>8.3997770000000006E-3</v>
       </c>
       <c r="G40">
-        <v>-0.99042934102956104</v>
+        <v>-1.0193631983039431</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
@@ -2955,7 +2952,7 @@
         <v>8.2779288000000006E-2</v>
       </c>
       <c r="G42">
-        <v>-1.0746651535384391</v>
+        <v>-1.084992596032458</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
@@ -2978,7 +2975,7 @@
         <v>1.3843718E-2</v>
       </c>
       <c r="G43">
-        <v>-0.99999999999999911</v>
+        <v>-0.99999999999999856</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
@@ -2998,7 +2995,7 @@
         <v>0.91434626799999996</v>
       </c>
       <c r="F44">
-        <v>14.7417194613039</v>
+        <v>0.14741719461303901</v>
       </c>
       <c r="G44">
         <v>-1</v>
@@ -3024,7 +3021,7 @@
         <v>9.3276440000000002E-2</v>
       </c>
       <c r="G45">
-        <v>-0.73995775828290788</v>
+        <v>-0.74081117030174315</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
@@ -3047,7 +3044,7 @@
         <v>2.9448841E-2</v>
       </c>
       <c r="G46">
-        <v>-1.0200285566083649</v>
+        <v>-1.0263289852412469</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
@@ -3067,10 +3064,10 @@
         <v>-0.14302638300000001</v>
       </c>
       <c r="F47">
-        <v>65.733047569623494</v>
+        <v>0.65733047569623493</v>
       </c>
       <c r="G47">
-        <v>-0.80000000000000437</v>
+        <v>-0.20000000000000079</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
@@ -3093,7 +3090,7 @@
         <v>1.3328486E-2</v>
       </c>
       <c r="G48">
-        <v>-1.0303225778194181</v>
+        <v>-1.048391102008249</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
@@ -3101,22 +3098,22 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>43070.593399999998</v>
+        <v>43569.173410000003</v>
       </c>
       <c r="D49">
-        <v>162.84233660000001</v>
+        <v>155.86191539999999</v>
       </c>
       <c r="E49">
-        <v>0.64724230199999999</v>
+        <v>0.64315882099999999</v>
       </c>
       <c r="F49">
-        <v>6.8115643000000003E-2</v>
+        <v>6.4048338999999996E-2</v>
       </c>
       <c r="G49">
-        <v>2.3731017151362721E-15</v>
+        <v>-0.59999999999999865</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
@@ -3139,7 +3136,7 @@
         <v>7.231131E-3</v>
       </c>
       <c r="G50">
-        <v>-0.99999999999999378</v>
+        <v>-0.99999999999999489</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
@@ -3159,10 +3156,10 @@
         <v>0.82487194500000005</v>
       </c>
       <c r="F51">
-        <v>105.76311963458799</v>
+        <v>1.05763119634588</v>
       </c>
       <c r="G51">
-        <v>-0.80000000000000016</v>
+        <v>-0.19999999999999971</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
@@ -3182,10 +3179,10 @@
         <v>0.99433494</v>
       </c>
       <c r="F52">
-        <v>0.90282275781676802</v>
+        <v>9.0282275781676802E-3</v>
       </c>
       <c r="G52">
-        <v>-0.99999999999999456</v>
+        <v>-0.99999999999999467</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
@@ -3208,7 +3205,7 @@
         <v>14.44117035</v>
       </c>
       <c r="G53">
-        <v>-1.1114879091234411</v>
+        <v>-0.30732658223901588</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
@@ -3228,10 +3225,10 @@
         <v>0.92283657299999999</v>
       </c>
       <c r="F54">
-        <v>2.0331360169289501</v>
+        <v>2.0331360169289499E-2</v>
       </c>
       <c r="G54">
-        <v>-0.58025294631144975</v>
+        <v>-0.78928236308965083</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
@@ -3254,7 +3251,7 @@
         <v>3.9646320000000001E-3</v>
       </c>
       <c r="G55">
-        <v>-1.1043879656652471</v>
+        <v>-1.1579355812643279</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
@@ -3277,7 +3274,7 @@
         <v>6.2729600000000002E-3</v>
       </c>
       <c r="G56">
-        <v>-0.80181301022686458</v>
+        <v>-0.8510636880511302</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
@@ -3300,7 +3297,7 @@
         <v>1.2161366E-2</v>
       </c>
       <c r="G57">
-        <v>-1.0275181987435771</v>
+        <v>-1.042605651957998</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
@@ -3308,22 +3305,22 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C58">
-        <v>86.865406239999999</v>
+        <v>177.51847509999999</v>
       </c>
       <c r="D58">
-        <v>8.6981875590000008</v>
+        <v>7.8383868210000003</v>
       </c>
       <c r="E58">
-        <v>-5.841521749</v>
+        <v>-12.98135991</v>
       </c>
       <c r="F58">
-        <v>25.781148922039701</v>
+        <v>0.23505756051177601</v>
       </c>
       <c r="G58">
-        <v>-2.6367796834847468E-16</v>
+        <v>-0.60000000000000009</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
@@ -3346,7 +3343,7 @@
         <v>0.88171302600000001</v>
       </c>
       <c r="G59">
-        <v>-0.71766918431804194</v>
+        <v>-0.71604587534281128</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
@@ -3369,7 +3366,7 @@
         <v>9.353676E-3</v>
       </c>
       <c r="G60">
-        <v>-0.72998609458189501</v>
+        <v>-0.79718433534552458</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
@@ -3392,7 +3389,7 @@
         <v>2.7712984E-2</v>
       </c>
       <c r="G61">
-        <v>-0.95645085866948287</v>
+        <v>-1.023775373618375</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
@@ -3415,7 +3412,7 @@
         <v>5.0667739999999996E-3</v>
       </c>
       <c r="G62">
-        <v>-1.375774850937286</v>
+        <v>-1.3816105479406779</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
@@ -3438,7 +3435,7 @@
         <v>0.70576106999999999</v>
       </c>
       <c r="G63">
-        <v>-1.024277427986553</v>
+        <v>-1.026313884421088</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
@@ -3461,7 +3458,7 @@
         <v>4.288076E-3</v>
       </c>
       <c r="G64">
-        <v>-1.147800662637511</v>
+        <v>-1.333414844059482</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
@@ -3484,7 +3481,7 @@
         <v>1.7603305999999999E-2</v>
       </c>
       <c r="G65">
-        <v>-0.99540382208701483</v>
+        <v>-1.0312222736841881</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
@@ -3507,7 +3504,7 @@
         <v>1.5768343000000001E-2</v>
       </c>
       <c r="G66">
-        <v>-1.0056419112852311</v>
+        <v>-1.0098087271635301</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
@@ -3530,7 +3527,7 @@
         <v>0.78275629400000002</v>
       </c>
       <c r="G67">
-        <v>-0.91899146963384404</v>
+        <v>-0.92046844197182742</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
@@ -3550,10 +3547,10 @@
         <v>0.73322486899999995</v>
       </c>
       <c r="F68">
-        <v>5.5340954059116498</v>
+        <v>5.5340954059116501E-2</v>
       </c>
       <c r="G68">
-        <v>-0.50708048965516128</v>
+        <v>-0.27146026267124063</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
@@ -3576,7 +3573,7 @@
         <v>4.6549419999999996E-3</v>
       </c>
       <c r="G69">
-        <v>-1.2022777122111981</v>
+        <v>-1.310573816536732</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
@@ -3599,7 +3596,7 @@
         <v>1.1042774E-2</v>
       </c>
       <c r="G70">
-        <v>-0.62648778154240414</v>
+        <v>-0.65116381655031497</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
@@ -3622,7 +3619,7 @@
         <v>2.9093349999999999E-3</v>
       </c>
       <c r="G71">
-        <v>-1</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
@@ -3630,22 +3627,22 @@
         <v>81</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C72">
-        <v>260.16610689999999</v>
+        <v>11899.313990000001</v>
       </c>
       <c r="D72">
-        <v>15.032516080000001</v>
+        <v>72.869450180000001</v>
       </c>
       <c r="E72">
-        <v>-146.60514209999999</v>
+        <v>0.22355291899999999</v>
       </c>
       <c r="F72">
-        <v>531.15960633500401</v>
+        <v>0.17825295899999999</v>
       </c>
       <c r="G72">
-        <v>-0.59047581866967669</v>
+        <v>-0.39517903714182978</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
@@ -3653,22 +3650,22 @@
         <v>82</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C73">
-        <v>0.17048828299999999</v>
+        <v>317.55820690000002</v>
       </c>
       <c r="D73">
-        <v>0.378328679</v>
+        <v>13.786981129999999</v>
       </c>
       <c r="E73">
-        <v>-0.660277365</v>
+        <v>-6.5632813529999998</v>
       </c>
       <c r="F73">
-        <v>60.194840975652603</v>
+        <v>0.26296670999999999</v>
       </c>
       <c r="G73">
-        <v>-0.56327378585220633</v>
+        <v>-0.7329404645810228</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
@@ -3688,10 +3685,10 @@
         <v>0.53371575100000002</v>
       </c>
       <c r="F74">
-        <v>38.578509849189999</v>
+        <v>0.38578509849190001</v>
       </c>
       <c r="G74">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999967</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
@@ -3714,7 +3711,7 @@
         <v>1.3948294E-2</v>
       </c>
       <c r="G75">
-        <v>-1.014973466669514</v>
+        <v>-1.017779625333751</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
@@ -3737,7 +3734,7 @@
         <v>1.2110114999999999E-2</v>
       </c>
       <c r="G76">
-        <v>-1.395329205091838</v>
+        <v>-1.343508260073051</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
@@ -3757,7 +3754,7 @@
         <v>0.51734466700000004</v>
       </c>
       <c r="F77">
-        <v>14.5345370895614</v>
+        <v>0.145345370895614</v>
       </c>
       <c r="G77">
         <v>-1</v>
@@ -3783,7 +3780,7 @@
         <v>1.0839486000000001E-2</v>
       </c>
       <c r="G78">
-        <v>-0.79999999999999383</v>
+        <v>-0.19999999999999371</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
@@ -3803,10 +3800,10 @@
         <v>0.523565485</v>
       </c>
       <c r="F79">
-        <v>39.7866703882232</v>
+        <v>0.397866703882232</v>
       </c>
       <c r="G79">
-        <v>-0.99999999999999711</v>
+        <v>-0.99999999999999922</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
@@ -3829,7 +3826,7 @@
         <v>4.1763263000000002E-2</v>
       </c>
       <c r="G80">
-        <v>-1.4504306699639109</v>
+        <v>-1.618686085462854</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
@@ -3875,7 +3872,7 @@
         <v>1.0038916E-2</v>
       </c>
       <c r="G82">
-        <v>-1.018393417372504</v>
+        <v>-1.0386368612048931</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
@@ -3898,7 +3895,7 @@
         <v>4.3505870000000004E-3</v>
       </c>
       <c r="G83">
-        <v>-1.155626714706609</v>
+        <v>-1.1522345380700481</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
@@ -3921,7 +3918,7 @@
         <v>1.1757319E-2</v>
       </c>
       <c r="G84">
-        <v>-0.76899462209459502</v>
+        <v>-0.81802544156195511</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
@@ -3967,7 +3964,7 @@
         <v>0.121750762</v>
       </c>
       <c r="G86">
-        <v>-1.1493827122435609</v>
+        <v>-1.115625053364909</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
@@ -3990,7 +3987,7 @@
         <v>6.7449960579999999</v>
       </c>
       <c r="G87">
-        <v>-1.0823140730256009</v>
+        <v>-1.0568941858395431</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
@@ -4013,7 +4010,7 @@
         <v>9.6253439999999992E-3</v>
       </c>
       <c r="G88">
-        <v>-0.99999999999999989</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
@@ -4021,22 +4018,22 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C89">
-        <v>3.0436365999999999E-2</v>
+        <v>11.124916069999999</v>
       </c>
       <c r="D89">
-        <v>0.134735033</v>
+        <v>2.5308504470000002</v>
       </c>
       <c r="E89">
-        <v>0.90624834499999996</v>
+        <v>0.99402963799999999</v>
       </c>
       <c r="F89">
-        <v>1.91016441502297</v>
+        <v>2.9265129999999999E-3</v>
       </c>
       <c r="G89">
-        <v>-0.44530748481195859</v>
+        <v>-0.56573061187060991</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
@@ -4059,7 +4056,7 @@
         <v>8.43789E-3</v>
       </c>
       <c r="G90">
-        <v>-1.0628096834646781</v>
+        <v>-1.121876116358312</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
@@ -4082,7 +4079,7 @@
         <v>1.2229139E-2</v>
       </c>
       <c r="G91">
-        <v>-1</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
@@ -4102,7 +4099,7 @@
         <v>-3.5926997300000001</v>
       </c>
       <c r="F92">
-        <v>36.328486296178603</v>
+        <v>0.36328486296178603</v>
       </c>
       <c r="G92">
         <v>-1.000000000000002</v>
@@ -4151,7 +4148,7 @@
         <v>1.8590575000000002E-2</v>
       </c>
       <c r="G94">
-        <v>-1</v>
+        <v>-1.0000000000000011</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.35">
@@ -4197,7 +4194,7 @@
         <v>5.0226539999999997E-3</v>
       </c>
       <c r="G96">
-        <v>-0.95735328959468469</v>
+        <v>-1.1276333290833349</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.35">
@@ -4220,7 +4217,7 @@
         <v>4.9479839999999999E-3</v>
       </c>
       <c r="G97">
-        <v>-0.94060478818373927</v>
+        <v>-1.016934067278741</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
@@ -4243,7 +4240,7 @@
         <v>1.9792292999999999E-2</v>
       </c>
       <c r="G98">
-        <v>-1.071609848512086</v>
+        <v>-1.129547584138417</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
@@ -4263,10 +4260,10 @@
         <v>-8.4196409209999992</v>
       </c>
       <c r="F99">
-        <v>970.25410221403297</v>
+        <v>9.7025410221403305</v>
       </c>
       <c r="G99">
-        <v>-0.8000000000000026</v>
+        <v>-0.19999999999999049</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
@@ -4286,10 +4283,10 @@
         <v>-4.4849751E-2</v>
       </c>
       <c r="F100">
-        <v>-35.986121106405299</v>
+        <v>-0.359861211064053</v>
       </c>
       <c r="G100">
-        <v>-0.19999999998377371</v>
+        <v>-0.19999999999973689</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
@@ -4309,10 +4306,10 @@
         <v>0.35256827299999999</v>
       </c>
       <c r="F101">
-        <v>7.8275428585414</v>
+        <v>7.8275428585414003E-2</v>
       </c>
       <c r="G101">
-        <v>-1</v>
+        <v>-0.99999999999999978</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
@@ -4358,7 +4355,7 @@
         <v>4.3670569999999997E-3</v>
       </c>
       <c r="G103">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999978</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
@@ -4378,7 +4375,7 @@
         <v>-2.2937291599999998</v>
       </c>
       <c r="F104">
-        <v>324.22678335355698</v>
+        <v>3.2422678335355699</v>
       </c>
       <c r="G104">
         <v>-0.99999999999999944</v>
@@ -4427,7 +4424,7 @@
         <v>0.189355882</v>
       </c>
       <c r="G106">
-        <v>-1.0000000000000011</v>
+        <v>-1.000000000000004</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
@@ -4435,22 +4432,22 @@
         <v>116</v>
       </c>
       <c r="B107" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C107">
-        <v>8.0511174539999999</v>
+        <v>787.3020593</v>
       </c>
       <c r="D107">
-        <v>1.3776407850000001</v>
+        <v>20.601972459999999</v>
       </c>
       <c r="E107">
-        <v>6.3088953000000003E-2</v>
+        <v>0.88423982899999998</v>
       </c>
       <c r="F107">
-        <v>17.078490897154602</v>
+        <v>1.8518127999999998E-2</v>
       </c>
       <c r="G107">
-        <v>-0.36188390402265819</v>
+        <v>-0.5784594558014553</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
@@ -4470,10 +4467,10 @@
         <v>-15.81538866</v>
       </c>
       <c r="F108">
-        <v>4333.2942932147498</v>
+        <v>43.332942932147503</v>
       </c>
       <c r="G108">
-        <v>-1</v>
+        <v>-0.99999999999999944</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
@@ -4493,7 +4490,7 @@
         <v>-50.54180495</v>
       </c>
       <c r="F109">
-        <v>1976.50871417644</v>
+        <v>19.765087141764401</v>
       </c>
       <c r="G109">
         <v>-1</v>
@@ -4516,10 +4513,10 @@
         <v>-0.48801684000000001</v>
       </c>
       <c r="F110">
-        <v>1916.51057024845</v>
+        <v>19.1651057024845</v>
       </c>
       <c r="G110">
-        <v>-0.99999999999999956</v>
+        <v>-1.000000000000002</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
@@ -4527,22 +4524,22 @@
         <v>120</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C111">
-        <v>4.6045088999999997E-2</v>
+        <v>0.46730602700000001</v>
       </c>
       <c r="D111">
-        <v>0.200546475</v>
+        <v>0.55169493599999997</v>
       </c>
       <c r="E111">
-        <v>-19.47562413</v>
+        <v>0.91135690599999997</v>
       </c>
       <c r="F111">
-        <v>40.4077731229035</v>
+        <v>1.1917048E-2</v>
       </c>
       <c r="G111">
-        <v>-0.66590113859854994</v>
+        <v>-0.56111756938572899</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
@@ -4562,10 +4559,10 @@
         <v>0.64746972700000005</v>
       </c>
       <c r="F112">
-        <v>466.17227883946401</v>
+        <v>4.6617227883946404</v>
       </c>
       <c r="G112">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999745</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
@@ -4588,7 +4585,7 @@
         <v>1.1120751999999999E-2</v>
       </c>
       <c r="G113">
-        <v>-0.99999999999998956</v>
+        <v>-0.9999999999999889</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
@@ -4634,7 +4631,7 @@
         <v>7.8973940000000003E-3</v>
       </c>
       <c r="G115">
-        <v>-1.216752164224957</v>
+        <v>-1.2752386007788039</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
@@ -4657,7 +4654,7 @@
         <v>6.3772120000000002E-3</v>
       </c>
       <c r="G116">
-        <v>-1.009161090438295</v>
+        <v>-1.032284341002343</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
@@ -4677,7 +4674,7 @@
         <v>-0.23784755799999999</v>
       </c>
       <c r="F117">
-        <v>22.562569489295399</v>
+        <v>0.225625694892954</v>
       </c>
       <c r="G117">
         <v>-1</v>
@@ -4700,7 +4697,7 @@
         <v>-0.58463809600000005</v>
       </c>
       <c r="F118">
-        <v>46.515810409463199</v>
+        <v>0.46515810409463199</v>
       </c>
       <c r="G118">
         <v>-1.0000000000000011</v>
@@ -4726,7 +4723,7 @@
         <v>6.1698910000000003E-3</v>
       </c>
       <c r="G119">
-        <v>-0.99999999999999933</v>
+        <v>-0.99999999999999878</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
@@ -4749,7 +4746,7 @@
         <v>3.7444520000000002E-2</v>
       </c>
       <c r="G120">
-        <v>-1.031514404718346</v>
+        <v>-1.032774548419396</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
@@ -4757,22 +4754,22 @@
         <v>130</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C121">
-        <v>28582.513660000001</v>
+        <v>44640.590239999998</v>
       </c>
       <c r="D121">
-        <v>122.5211192</v>
+        <v>106.1698774</v>
       </c>
       <c r="E121">
-        <v>0.99022944000000002</v>
+        <v>0.98474019599999996</v>
       </c>
       <c r="F121">
-        <v>6.5200529999999996E-3</v>
+        <v>5.5170499999999999E-3</v>
       </c>
       <c r="G121">
-        <v>-1.1495252046851281</v>
+        <v>-1.0720782646443561</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
@@ -4795,7 +4792,7 @@
         <v>3.204532E-3</v>
       </c>
       <c r="G122">
-        <v>-1.117614920493587</v>
+        <v>-1.134804572563906</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
@@ -4818,7 +4815,7 @@
         <v>1.1705764E-2</v>
       </c>
       <c r="G123">
-        <v>-1.0357978754306589</v>
+        <v>-1.061007068592722</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
@@ -4841,7 +4838,7 @@
         <v>5.3787080000000003E-3</v>
       </c>
       <c r="G124">
-        <v>-1.1138370918119509</v>
+        <v>-1.225236978758071</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
@@ -4861,10 +4858,10 @@
         <v>0.97798200099999999</v>
       </c>
       <c r="F125">
-        <v>1.4993080789567099</v>
+        <v>1.49930807895671E-2</v>
       </c>
       <c r="G125">
-        <v>-0.99999999999999922</v>
+        <v>-0.99999999999999933</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
@@ -4907,10 +4904,10 @@
         <v>0.96399480500000001</v>
       </c>
       <c r="F127">
-        <v>1.0290060951553199</v>
+        <v>1.0290060951553199E-2</v>
       </c>
       <c r="G127">
-        <v>-1</v>
+        <v>-0.99999999999999967</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
@@ -4933,7 +4930,7 @@
         <v>6.33214E-3</v>
       </c>
       <c r="G128">
-        <v>-0.93134241484415459</v>
+        <v>-0.96168447514448741</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
@@ -4956,7 +4953,7 @@
         <v>8.7016420000000008E-3</v>
       </c>
       <c r="G129">
-        <v>-1.185742521954305</v>
+        <v>-1.2587245731246539</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
@@ -4979,7 +4976,7 @@
         <v>1.3680576999999999E-2</v>
       </c>
       <c r="G130">
-        <v>-1</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
@@ -5002,7 +4999,7 @@
         <v>3.453547E-3</v>
       </c>
       <c r="G131">
-        <v>-0.88947671604153133</v>
+        <v>-0.9740421843357836</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
@@ -5025,7 +5022,7 @@
         <v>3.891402E-3</v>
       </c>
       <c r="G132">
-        <v>-1.123119646372253</v>
+        <v>-1.286723331933924</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
@@ -5045,7 +5042,7 @@
         <v>0.53903295200000001</v>
       </c>
       <c r="F133">
-        <v>3.0119660314104899</v>
+        <v>3.0119660314104901E-2</v>
       </c>
       <c r="G133">
         <v>-1</v>
@@ -5071,7 +5068,7 @@
         <v>1.6630573999999999E-2</v>
       </c>
       <c r="G134">
-        <v>-1.1071106517807989</v>
+        <v>-1.275635528493763</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
@@ -5117,7 +5114,7 @@
         <v>1.4970005999999999E-2</v>
       </c>
       <c r="G136">
-        <v>-1.0089563550161069</v>
+        <v>-0.98717141364746264</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
@@ -5160,10 +5157,10 @@
         <v>2.5632622000000001E-2</v>
       </c>
       <c r="F138">
-        <v>8.1029403624158292</v>
+        <v>8.1029403624158294E-2</v>
       </c>
       <c r="G138">
-        <v>1.554312234475219E-15</v>
+        <v>-0.59999999999999976</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
@@ -5171,22 +5168,22 @@
         <v>148</v>
       </c>
       <c r="B139" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C139">
-        <v>3.547539134</v>
+        <v>16667.053810000001</v>
       </c>
       <c r="D139">
-        <v>1.4917838779999999</v>
+        <v>92.720054610000005</v>
       </c>
       <c r="E139">
-        <v>-1.68322024</v>
+        <v>-0.55671662499999996</v>
       </c>
       <c r="F139">
-        <v>11.962807294304</v>
+        <v>5.7698049000000001E-2</v>
       </c>
       <c r="G139">
-        <v>-0.42426108743218283</v>
+        <v>-1.7335328187453041E-3</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
@@ -5209,7 +5206,7 @@
         <v>5.3368914000000003E-2</v>
       </c>
       <c r="G140">
-        <v>-1.2185754502724691</v>
+        <v>-1.2997291993658731</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
@@ -5232,7 +5229,7 @@
         <v>4.7277810000000003E-3</v>
       </c>
       <c r="G141">
-        <v>-1.0076998345160351</v>
+        <v>-1.109507152073024</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
@@ -5255,7 +5252,7 @@
         <v>2.2216263999999999E-2</v>
       </c>
       <c r="G142">
-        <v>-0.96469117787539582</v>
+        <v>-0.98472572978355788</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
@@ -5278,7 +5275,7 @@
         <v>4.1822179999999997E-3</v>
       </c>
       <c r="G143">
-        <v>-1.610072674378201</v>
+        <v>-1.6804594388244269</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
@@ -5298,10 +5295,10 @@
         <v>-0.683783739</v>
       </c>
       <c r="F144">
-        <v>8.9449082312455008</v>
+        <v>8.9449082312455006E-2</v>
       </c>
       <c r="G144">
-        <v>-1.022642149262269</v>
+        <v>-0.44795672363543088</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
@@ -5324,7 +5321,7 @@
         <v>2.9801570000000002E-3</v>
       </c>
       <c r="G145">
-        <v>-0.98872393576914896</v>
+        <v>-0.99508555751022454</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
@@ -5347,7 +5344,7 @@
         <v>7.7237750000000004E-3</v>
       </c>
       <c r="G146">
-        <v>-1.4942591587624421</v>
+        <v>-1.5679801821938399</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
@@ -5370,7 +5367,7 @@
         <v>9.6209580000000006E-3</v>
       </c>
       <c r="G147">
-        <v>-0.96971073027027965</v>
+        <v>-1.0135051345891199</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
@@ -5393,7 +5390,7 @@
         <v>1.2568184E-2</v>
       </c>
       <c r="G148">
-        <v>-1.0084804910651159</v>
+        <v>-1.0104895206404061</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
@@ -5413,10 +5410,10 @@
         <v>0.98744098499999999</v>
       </c>
       <c r="F149">
-        <v>1.27031738308596</v>
+        <v>1.27031738308596E-2</v>
       </c>
       <c r="G149">
-        <v>-1.0000000000000051</v>
+        <v>-1.000000000000006</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
@@ -5439,7 +5436,7 @@
         <v>5.4935089999999997E-3</v>
       </c>
       <c r="G150">
-        <v>-1.0748729146015039</v>
+        <v>-1.023904206933677</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
@@ -5462,7 +5459,7 @@
         <v>8.2495850000000003E-3</v>
       </c>
       <c r="G151">
-        <v>-0.63329728173294952</v>
+        <v>-0.66292839413433102</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
@@ -5485,7 +5482,7 @@
         <v>6.2974160000000001E-3</v>
       </c>
       <c r="G152">
-        <v>-1.2683303359031459</v>
+        <v>-1.385056203563368</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
@@ -5505,10 +5502,10 @@
         <v>0.96708566600000001</v>
       </c>
       <c r="F153">
-        <v>1.54171674684882</v>
+        <v>1.54171674684882E-2</v>
       </c>
       <c r="G153">
-        <v>-0.99999999999999989</v>
+        <v>-0.99999999999999978</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
@@ -5531,7 +5528,7 @@
         <v>3.9974257999999999E-2</v>
       </c>
       <c r="G154">
-        <v>-0.46375473123603478</v>
+        <v>-0.67350257115147816</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
@@ -5551,10 +5548,10 @@
         <v>0.95449168100000004</v>
       </c>
       <c r="F155">
-        <v>2.2359332390711399</v>
+        <v>2.23593323907114E-2</v>
       </c>
       <c r="G155">
-        <v>-0.59206693344300687</v>
+        <v>-0.66475750295766767</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
@@ -5577,7 +5574,7 @@
         <v>3.1949000000000001E-3</v>
       </c>
       <c r="G156">
-        <v>-3.9385161798577428E-14</v>
+        <v>-0.60000000000003606</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
@@ -5600,7 +5597,7 @@
         <v>3.5585431000000001E-2</v>
       </c>
       <c r="G157">
-        <v>-0.70023996776079755</v>
+        <v>-0.70679088407228585</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
@@ -5623,7 +5620,7 @@
         <v>3.3780390000000002E-3</v>
       </c>
       <c r="G158">
-        <v>-1.1580731148690431</v>
+        <v>-1.198314309702226</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
@@ -5646,7 +5643,7 @@
         <v>1.387952E-3</v>
       </c>
       <c r="G159">
-        <v>-1.058544382738698</v>
+        <v>-1.1223973128180189</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
@@ -5669,7 +5666,7 @@
         <v>1.2033449E-2</v>
       </c>
       <c r="G160">
-        <v>-0.96697830345510494</v>
+        <v>-0.98127342193240386</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
@@ -5692,7 +5689,7 @@
         <v>7.6944159999999999E-3</v>
       </c>
       <c r="G161">
-        <v>-0.84459319017615608</v>
+        <v>-0.92406059099086157</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
@@ -5712,7 +5709,7 @@
         <v>0.60072071599999999</v>
       </c>
       <c r="F162">
-        <v>2.4852107517433901</v>
+        <v>2.48521075174339E-2</v>
       </c>
       <c r="G162">
         <v>-1</v>
@@ -5738,7 +5735,7 @@
         <v>7.0289530000000001E-3</v>
       </c>
       <c r="G163">
-        <v>-0.94535275571170374</v>
+        <v>-0.98844634596730419</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
@@ -5761,7 +5758,7 @@
         <v>7.2570588000000005E-2</v>
       </c>
       <c r="G164">
-        <v>-1.0133966833443251</v>
+        <v>-0.99962719178632309</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
@@ -5784,7 +5781,7 @@
         <v>6.1617485999999999E-2</v>
       </c>
       <c r="G165">
-        <v>-0.68445924778063583</v>
+        <v>-0.61700273590540078</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
@@ -5830,7 +5827,7 @@
         <v>0.74621356599999999</v>
       </c>
       <c r="G167">
-        <v>-1.0034150943612841</v>
+        <v>-1.174653142767992</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
@@ -5853,7 +5850,7 @@
         <v>8.7769149999999997E-3</v>
       </c>
       <c r="G168">
-        <v>-1.544919086766503</v>
+        <v>-1.6295299262701</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
@@ -5876,7 +5873,7 @@
         <v>8.6593769999999994E-3</v>
       </c>
       <c r="G169">
-        <v>-1.1152129794197321</v>
+        <v>-1.220653226039387</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
@@ -5899,7 +5896,7 @@
         <v>1.4575937000000001E-2</v>
       </c>
       <c r="G170">
-        <v>-1.038562662964384</v>
+        <v>-1.0598627048706799</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
@@ -5919,7 +5916,7 @@
         <v>-10.01941435</v>
       </c>
       <c r="F171">
-        <v>96.372228670592094</v>
+        <v>0.96372228670592097</v>
       </c>
       <c r="G171">
         <v>-1</v>
@@ -5945,7 +5942,7 @@
         <v>2.3795029999999998E-3</v>
       </c>
       <c r="G172">
-        <v>-1.136541797695654</v>
+        <v>-1.182119213434756</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
@@ -5968,7 +5965,7 @@
         <v>5.1954119999999999E-3</v>
       </c>
       <c r="G173">
-        <v>-0.73182159297838334</v>
+        <v>-0.76091254852814527</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
@@ -5991,7 +5988,7 @@
         <v>8.5650559999999997E-3</v>
       </c>
       <c r="G174">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999933</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
@@ -6037,7 +6034,7 @@
         <v>3.3467190000000002E-3</v>
       </c>
       <c r="G176">
-        <v>-0.99999999999998657</v>
+        <v>-0.99999999999998679</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
@@ -6060,7 +6057,7 @@
         <v>4.8170082000000003E-2</v>
       </c>
       <c r="G177">
-        <v>-0.96707680887894398</v>
+        <v>-1.0388040315217331</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
@@ -6083,7 +6080,7 @@
         <v>1.462018E-2</v>
       </c>
       <c r="G178">
-        <v>-0.99736144665904392</v>
+        <v>-1.0018493347446129</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
@@ -6106,7 +6103,7 @@
         <v>6.1910357999999999E-2</v>
       </c>
       <c r="G179">
-        <v>-1.2455652200195411</v>
+        <v>-1.2217175133402109</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.35">
@@ -6129,7 +6126,7 @@
         <v>6.5683479999999999E-3</v>
       </c>
       <c r="G180">
-        <v>-1.1011943123015691</v>
+        <v>-1.091732554768774</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
@@ -6152,7 +6149,7 @@
         <v>5.579011E-3</v>
       </c>
       <c r="G181">
-        <v>-0.67263831620965175</v>
+        <v>-0.69867846503268627</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
@@ -6160,22 +6157,22 @@
         <v>191</v>
       </c>
       <c r="B182" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C182">
-        <v>1749.444056</v>
+        <v>2410.0526049999999</v>
       </c>
       <c r="D182">
-        <v>38.418044270000003</v>
+        <v>41.214806420000002</v>
       </c>
       <c r="E182">
-        <v>0.99421089500000004</v>
+        <v>0.992024868</v>
       </c>
       <c r="F182">
-        <v>1.2603422929999999</v>
+        <v>0.65221388199999997</v>
       </c>
       <c r="G182">
-        <v>-1.005980071813187</v>
+        <v>-1.0065764597409459</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
@@ -6195,10 +6192,10 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>48.344583694587598</v>
+        <v>0.48344583694587601</v>
       </c>
       <c r="G183">
-        <v>-0.91123964307406191</v>
+        <v>-0.8628511316559635</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
@@ -6221,7 +6218,7 @@
         <v>4.2681749999999999E-3</v>
       </c>
       <c r="G184">
-        <v>-1.2057665539286571</v>
+        <v>-1.2843995238709609</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
@@ -6241,7 +6238,7 @@
         <v>-5.0866091789999999</v>
       </c>
       <c r="F185">
-        <v>30.872566736297301</v>
+        <v>0.30872566736297302</v>
       </c>
       <c r="G185">
         <v>-1</v>
@@ -6267,7 +6264,7 @@
         <v>5.2412822999999997E-2</v>
       </c>
       <c r="G186">
-        <v>-0.7654380010323335</v>
+        <v>-0.78499437642067615</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
@@ -6290,7 +6287,7 @@
         <v>7.1729009999999998E-3</v>
       </c>
       <c r="G187">
-        <v>-0.95183184695153411</v>
+        <v>-1.1184247449480551</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
@@ -6313,7 +6310,7 @@
         <v>0.184366639</v>
       </c>
       <c r="G188">
-        <v>-1.1087105255283529</v>
+        <v>-1.152076081270933</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
@@ -6356,7 +6353,7 @@
         <v>-4.594442924</v>
       </c>
       <c r="F190">
-        <v>54.467027258256699</v>
+        <v>0.54467027258256695</v>
       </c>
       <c r="G190">
         <v>-1</v>
@@ -6382,7 +6379,7 @@
         <v>6.2368759999999997E-3</v>
       </c>
       <c r="G191">
-        <v>-1.1292091501846739</v>
+        <v>-1.232558226965943</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
@@ -6402,10 +6399,10 @@
         <v>0.20583488899999999</v>
       </c>
       <c r="F192">
-        <v>122.212802986432</v>
+        <v>1.22212802986432</v>
       </c>
       <c r="G192">
-        <v>-4.5796699765787707E-16</v>
+        <v>-0.60000000000000064</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.35">
@@ -6428,7 +6425,7 @@
         <v>0.12743365600000001</v>
       </c>
       <c r="G193">
-        <v>-0.93371829455498589</v>
+        <v>-0.95286487395158515</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.35">
@@ -6451,7 +6448,7 @@
         <v>7.4901200000000003E-3</v>
       </c>
       <c r="G194">
-        <v>-1.136568188470984</v>
+        <v>-1.2171817563443761</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.35">
@@ -6517,10 +6514,10 @@
         <v>0.96313864999999999</v>
       </c>
       <c r="F197">
-        <v>0.833041898285522</v>
+        <v>8.33041898285522E-3</v>
       </c>
       <c r="G197">
-        <v>-1</v>
+        <v>-1.0000000000000011</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.35">
@@ -6543,7 +6540,7 @@
         <v>5.0739599999999998E-3</v>
       </c>
       <c r="G198">
-        <v>-1.121759950412706</v>
+        <v>-1.1857317644102161</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.35">
@@ -6586,10 +6583,10 @@
         <v>-21.660770800000002</v>
       </c>
       <c r="F200">
-        <v>60.465530434925398</v>
+        <v>0.60465530434925396</v>
       </c>
       <c r="G200">
-        <v>-0.80957022102959331</v>
+        <v>-0.49998446204915642</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.35">
@@ -6609,10 +6606,10 @@
         <v>-0.24103039400000001</v>
       </c>
       <c r="F201">
-        <v>22.077096575395601</v>
+        <v>0.22077096575395599</v>
       </c>
       <c r="G201">
-        <v>-0.99999999999999989</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.35">
@@ -6632,7 +6629,7 @@
         <v>0.69860612</v>
       </c>
       <c r="F202">
-        <v>9.68798662930406</v>
+        <v>9.6879866293040601E-2</v>
       </c>
       <c r="G202">
         <v>-1</v>
@@ -6658,7 +6655,7 @@
         <v>1.9484774999999999E-2</v>
       </c>
       <c r="G203">
-        <v>-1.0224896262233441</v>
+        <v>-1.035943404172478</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.35">
@@ -6681,7 +6678,7 @@
         <v>1.176241519</v>
       </c>
       <c r="G204">
-        <v>-1.4497207765318501</v>
+        <v>-1.475504062691104</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.35">
@@ -6704,7 +6701,7 @@
         <v>2.5998150000000001E-3</v>
       </c>
       <c r="G205">
-        <v>-1.243131049255948</v>
+        <v>-1.3043874489484739</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.35">
@@ -6727,7 +6724,7 @@
         <v>1.0200348E-2</v>
       </c>
       <c r="G206">
-        <v>-0.99378941778396013</v>
+        <v>-0.99657178817614689</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.35">
@@ -6750,7 +6747,7 @@
         <v>2.250773E-2</v>
       </c>
       <c r="G207">
-        <v>-1.0264203312001301</v>
+        <v>-0.93611444514890096</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.35">
@@ -6770,10 +6767,10 @@
         <v>-1.0972896379999999</v>
       </c>
       <c r="F208">
-        <v>50.064011024163499</v>
+        <v>0.50064011024163502</v>
       </c>
       <c r="G208">
-        <v>-0.79888605787802858</v>
+        <v>-0.31800953226567258</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.35">
@@ -6796,7 +6793,7 @@
         <v>5.7930259999999997E-3</v>
       </c>
       <c r="G209">
-        <v>-0.70670485071506661</v>
+        <v>-0.73874649441263052</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.35">
@@ -6819,7 +6816,7 @@
         <v>1.4035949000000001E-2</v>
       </c>
       <c r="G210">
-        <v>-1.0070038062133451</v>
+        <v>-1.014635465971141</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.35">
@@ -6842,7 +6839,7 @@
         <v>1.1963448329999999</v>
       </c>
       <c r="G211">
-        <v>-1.2247871239503749</v>
+        <v>-1.373918254901636</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.35">
@@ -6865,7 +6862,7 @@
         <v>8.8398920000000002E-3</v>
       </c>
       <c r="G212">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999933</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.35">
@@ -6888,7 +6885,7 @@
         <v>4.5058099999999999E-3</v>
       </c>
       <c r="G213">
-        <v>-1.0874290418025749</v>
+        <v>-1.145617289222655</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.35">
@@ -6934,7 +6931,7 @@
         <v>5.5682689999999998E-3</v>
       </c>
       <c r="G215">
-        <v>-0.73329020332414596</v>
+        <v>-0.7323427492861756</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.35">
@@ -6954,7 +6951,7 @@
         <v>-0.81545618499999994</v>
       </c>
       <c r="F216">
-        <v>131.126751879209</v>
+        <v>1.3112675187920899</v>
       </c>
       <c r="G216">
         <v>-1</v>
@@ -6980,7 +6977,7 @@
         <v>5.616724E-3</v>
       </c>
       <c r="G217">
-        <v>-1.263759386546508</v>
+        <v>-1.3466052418430789</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.35">
@@ -7003,7 +7000,7 @@
         <v>4.6566300000000001E-3</v>
       </c>
       <c r="G218">
-        <v>-0.94122041719511773</v>
+        <v>-0.92902213653471299</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.35">
@@ -7026,7 +7023,7 @@
         <v>0.157436776</v>
       </c>
       <c r="G219">
-        <v>-0.88082853064721878</v>
+        <v>-0.94128754211598054</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.35">
@@ -7034,22 +7031,22 @@
         <v>229</v>
       </c>
       <c r="B220" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C220">
-        <v>0.484650311</v>
+        <v>21.15183777</v>
       </c>
       <c r="D220">
-        <v>0.475109212</v>
+        <v>2.9009118649999999</v>
       </c>
       <c r="E220">
-        <v>-0.81530839799999999</v>
+        <v>0.768702318</v>
       </c>
       <c r="F220">
-        <v>46.000517379833497</v>
+        <v>3.5430332000000002E-2</v>
       </c>
       <c r="G220">
-        <v>-0.51772558475587682</v>
+        <v>-0.39069960576555729</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
@@ -7072,7 +7069,7 @@
         <v>4.451315E-3</v>
       </c>
       <c r="G221">
-        <v>-0.96363462978476688</v>
+        <v>-0.99469146673769027</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -7095,7 +7092,7 @@
         <v>3.0696927999999998E-2</v>
       </c>
       <c r="G222">
-        <v>-0.85862658786326984</v>
+        <v>-0.89675904022957242</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.35">
@@ -7118,7 +7115,7 @@
         <v>1.4358019E-2</v>
       </c>
       <c r="G223">
-        <v>-0.71252436249536488</v>
+        <v>-0.71882395331256443</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.35">
@@ -7141,7 +7138,7 @@
         <v>3.0626324999999999E-2</v>
       </c>
       <c r="G224">
-        <v>-0.96761265966825405</v>
+        <v>-0.96934521879067426</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.35">
@@ -7164,7 +7161,7 @@
         <v>7.4433001999999998E-2</v>
       </c>
       <c r="G225">
-        <v>-1.0088124321103891</v>
+        <v>-1.0096517243582079</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.35">
@@ -7187,7 +7184,7 @@
         <v>4.4891030000000004E-3</v>
       </c>
       <c r="G226">
-        <v>-1.0245536501123089</v>
+        <v>-1.3831853539436809</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.35">
@@ -7207,10 +7204,10 @@
         <v>-520.82252630000005</v>
       </c>
       <c r="F227">
-        <v>396.51046391038801</v>
+        <v>3.9651046391038798</v>
       </c>
       <c r="G227">
-        <v>-0.58158553286652415</v>
+        <v>-0.85032932886817181</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
@@ -7233,7 +7230,7 @@
         <v>5.9456179999999997E-3</v>
       </c>
       <c r="G228">
-        <v>-0.99999999999998412</v>
+        <v>-0.99999999999998401</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.35">
@@ -7256,7 +7253,7 @@
         <v>2.5379719999999999E-3</v>
       </c>
       <c r="G229">
-        <v>-1.1529651176715829</v>
+        <v>-1.2509225153100481</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
@@ -7279,7 +7276,7 @@
         <v>6.46183E-3</v>
       </c>
       <c r="G230">
-        <v>-0.84943417155527723</v>
+        <v>-0.89975631606475337</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.35">
@@ -7302,7 +7299,7 @@
         <v>4.4408779999999997E-3</v>
       </c>
       <c r="G231">
-        <v>-1.0368688974050211</v>
+        <v>-1.102547771538507</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.35">
@@ -7325,7 +7322,7 @@
         <v>1.9481470000000001E-2</v>
       </c>
       <c r="G232">
-        <v>-0.7203361347558378</v>
+        <v>-0.72645148219177413</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.35">
@@ -7345,7 +7342,7 @@
         <v>-0.42463810499999999</v>
       </c>
       <c r="F233">
-        <v>928.38668571200003</v>
+        <v>9.2838668571199996</v>
       </c>
       <c r="G233">
         <v>-1</v>
@@ -7371,7 +7368,7 @@
         <v>7.4271629999999996E-3</v>
       </c>
       <c r="G234">
-        <v>-0.87689571385494425</v>
+        <v>-0.92877005551155456</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.35">
@@ -7391,10 +7388,10 @@
         <v>-8.1336473320000007</v>
       </c>
       <c r="F235">
-        <v>541435.67643746897</v>
+        <v>5414.3567643746901</v>
       </c>
       <c r="G235">
-        <v>-0.80000000000000138</v>
+        <v>-0.19999999999999959</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.35">
@@ -7440,7 +7437,7 @@
         <v>3.5268220000000002E-3</v>
       </c>
       <c r="G237">
-        <v>-1.41008822681687</v>
+        <v>-1.416977793299188</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.35">
@@ -7463,7 +7460,7 @@
         <v>0.12540849800000001</v>
       </c>
       <c r="G238">
-        <v>-0.19999999999999979</v>
+        <v>-0.19999999999999959</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.35">
@@ -7486,7 +7483,7 @@
         <v>2.6071699E-2</v>
       </c>
       <c r="G239">
-        <v>-0.99999999999999989</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.35">
@@ -7509,7 +7506,7 @@
         <v>5.1196669999999996E-3</v>
       </c>
       <c r="G240">
-        <v>-0.84040947923344922</v>
+        <v>-0.92384130656722041</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.35">
@@ -7532,7 +7529,7 @@
         <v>5.5361350000000002E-3</v>
       </c>
       <c r="G241">
-        <v>-0.76788531825138595</v>
+        <v>-0.94127677287726119</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.35">
@@ -7555,7 +7552,7 @@
         <v>5.6482989999999999E-3</v>
       </c>
       <c r="G242">
-        <v>-1.06594851789764</v>
+        <v>-1.120549961185239</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.35">
@@ -7575,10 +7572,10 @@
         <v>0.93190419099999999</v>
       </c>
       <c r="F243">
-        <v>1.5403218246391801</v>
+        <v>1.5403218246391801E-2</v>
       </c>
       <c r="G243">
-        <v>-1.000000000000006</v>
+        <v>-1.000000000000004</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.35">
@@ -7598,10 +7595,10 @@
         <v>-1.523553849</v>
       </c>
       <c r="F244">
-        <v>10.333440725017301</v>
+        <v>0.103334407250173</v>
       </c>
       <c r="G244">
-        <v>-0.99999999999999978</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.35">
@@ -7621,7 +7618,7 @@
         <v>0.89015186599999996</v>
       </c>
       <c r="F245">
-        <v>2.4421155448562399</v>
+        <v>2.4421155448562399E-2</v>
       </c>
       <c r="G245">
         <v>-1.0000000000000011</v>
@@ -7647,7 +7644,7 @@
         <v>7.496885E-3</v>
       </c>
       <c r="G246">
-        <v>-1.0115395778415719</v>
+        <v>-1.0178676199434069</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.35">
@@ -7670,7 +7667,7 @@
         <v>3.7278419999999999E-3</v>
       </c>
       <c r="G247">
-        <v>-1.0918899030184961</v>
+        <v>-1.160029190546739</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.35">
@@ -7693,7 +7690,7 @@
         <v>7.9862779999999994E-3</v>
       </c>
       <c r="G248">
-        <v>-1.384405030830669</v>
+        <v>-1.468844422215988</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.35">
@@ -7716,7 +7713,7 @@
         <v>1.2909014999999999E-2</v>
       </c>
       <c r="G249">
-        <v>-0.87871547273738559</v>
+        <v>-1.04435532430208</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.35">
@@ -7739,7 +7736,7 @@
         <v>7.8124470000000001E-3</v>
       </c>
       <c r="G250">
-        <v>-0.74063099915110575</v>
+        <v>-0.74551474110258398</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.35">
@@ -7762,7 +7759,7 @@
         <v>9.1772042999999998E-2</v>
       </c>
       <c r="G251">
-        <v>-0.88421767596877832</v>
+        <v>-0.90328157566155332</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.35">
@@ -7785,7 +7782,7 @@
         <v>5.7272879999999997E-3</v>
       </c>
       <c r="G252">
-        <v>-1.4822492507481999</v>
+        <v>-1.6170025042346989</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.35">
@@ -7808,7 +7805,7 @@
         <v>5.7330059999999997E-3</v>
       </c>
       <c r="G253">
-        <v>-1.5045624395003201</v>
+        <v>-1.5527671985845051</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.35">
@@ -7831,7 +7828,7 @@
         <v>2.4798542999999999E-2</v>
       </c>
       <c r="G254">
-        <v>-1.152642927727269</v>
+        <v>-1.150123533749712</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.35">
@@ -7854,7 +7851,7 @@
         <v>4.2246289999999997E-3</v>
       </c>
       <c r="G255">
-        <v>-1.334695607529925</v>
+        <v>-1.408870258884664</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.35">
@@ -7900,7 +7897,7 @@
         <v>5.2037560000000004E-3</v>
       </c>
       <c r="G257">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999978</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.35">
@@ -7923,7 +7920,7 @@
         <v>1.1473525E-2</v>
       </c>
       <c r="G258">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999967</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.35">
@@ -7946,7 +7943,7 @@
         <v>4.425216E-3</v>
       </c>
       <c r="G259">
-        <v>-1.0112156309843801</v>
+        <v>-1.142171647648228</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.35">
@@ -7969,7 +7966,7 @@
         <v>3.36477E-3</v>
       </c>
       <c r="G260">
-        <v>-1.1419066883449589</v>
+        <v>-1.1976371922989839</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.35">
@@ -7977,22 +7974,22 @@
         <v>270</v>
       </c>
       <c r="B261" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C261">
-        <v>37.43553404</v>
+        <v>49.559248410000002</v>
       </c>
       <c r="D261">
-        <v>4.4602932879999999</v>
+        <v>4.4035401959999998</v>
       </c>
       <c r="E261">
-        <v>0.987626483</v>
+        <v>0.98361924700000003</v>
       </c>
       <c r="F261">
-        <v>6.5167510000000003E-3</v>
+        <v>6.4797179999999998E-3</v>
       </c>
       <c r="G261">
-        <v>-0.84920855438929777</v>
+        <v>-0.93037495810617821</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
@@ -8012,10 +8009,10 @@
         <v>0.98825431699999999</v>
       </c>
       <c r="F262">
-        <v>1.0424778237680901</v>
+        <v>1.04247782376809E-2</v>
       </c>
       <c r="G262">
-        <v>-0.99999999999999878</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.35">
@@ -8058,7 +8055,7 @@
         <v>0.88667473399999996</v>
       </c>
       <c r="F264">
-        <v>5.5224873399695698</v>
+        <v>5.5224873399695701E-2</v>
       </c>
       <c r="G264">
         <v>-0.99999999999999756</v>
@@ -8084,7 +8081,7 @@
         <v>1.4972776E-2</v>
       </c>
       <c r="G265">
-        <v>-0.99999999999999944</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.35">
@@ -8107,7 +8104,7 @@
         <v>7.3178560000000002E-3</v>
       </c>
       <c r="G266">
-        <v>-0.90315718933157096</v>
+        <v>-0.97773928956492695</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.35">
@@ -8127,10 +8124,10 @@
         <v>0.529796551</v>
       </c>
       <c r="F267">
-        <v>128.34236189750999</v>
+        <v>1.2834236189751</v>
       </c>
       <c r="G267">
-        <v>-1</v>
+        <v>-1.0000000000000011</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.35">
@@ -8153,7 +8150,7 @@
         <v>0.25855716400000001</v>
       </c>
       <c r="G268">
-        <v>-0.64178093899000532</v>
+        <v>-0.60362459897208232</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.35">
@@ -8173,7 +8170,7 @@
         <v>0.50967913399999998</v>
       </c>
       <c r="F269">
-        <v>2.83584688650018</v>
+        <v>2.8358468865001801E-2</v>
       </c>
       <c r="G269">
         <v>-1</v>
@@ -8222,7 +8219,7 @@
         <v>5.5080959999999997E-3</v>
       </c>
       <c r="G271">
-        <v>-1.4180341696553069</v>
+        <v>-1.514881933855001</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.35">
@@ -8245,7 +8242,7 @@
         <v>6.6177509999999998E-3</v>
       </c>
       <c r="G272">
-        <v>-0.78077094189463814</v>
+        <v>-0.81815082329716649</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.35">
@@ -8268,7 +8265,7 @@
         <v>1.9488377000000001E-2</v>
       </c>
       <c r="G273">
-        <v>-1.1315817568022539</v>
+        <v>-1.18479676630932</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.35">
@@ -8291,7 +8288,7 @@
         <v>7.0689009999999998E-3</v>
       </c>
       <c r="G274">
-        <v>-0.70667513385369873</v>
+        <v>-0.71249058933568643</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.35">
@@ -8311,10 +8308,10 @@
         <v>0.99078091000000001</v>
       </c>
       <c r="F275">
-        <v>0.85135996629975097</v>
+        <v>8.5135996629975095E-3</v>
       </c>
       <c r="G275">
-        <v>-0.99999999999999911</v>
+        <v>-0.99999999999999889</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.35">
@@ -8337,7 +8334,7 @@
         <v>5.5134329999999999E-3</v>
       </c>
       <c r="G276">
-        <v>-1.323034590980523</v>
+        <v>-1.417719563472966</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.35">
@@ -8357,10 +8354,10 @@
         <v>0.88812517499999999</v>
       </c>
       <c r="F277">
-        <v>3.3616996461496398</v>
+        <v>3.36169964614964E-2</v>
       </c>
       <c r="G277">
-        <v>-0.80000000000000038</v>
+        <v>-0.20000000000000029</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.35">
@@ -8383,7 +8380,7 @@
         <v>4.508738E-3</v>
       </c>
       <c r="G278">
-        <v>-1.089446992261492</v>
+        <v>-1.2535048694905839</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
@@ -8403,7 +8400,7 @@
         <v>0.53194544099999996</v>
       </c>
       <c r="F279">
-        <v>2.5744625094635101</v>
+        <v>2.5744625094635099E-2</v>
       </c>
       <c r="G279">
         <v>-1</v>
@@ -8426,10 +8423,10 @@
         <v>-0.79344472099999996</v>
       </c>
       <c r="F280">
-        <v>18.359110616455101</v>
+        <v>0.18359110616455099</v>
       </c>
       <c r="G280">
-        <v>-1.0000000000000011</v>
+        <v>-1.000000000000002</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.35">
@@ -8452,7 +8449,7 @@
         <v>2.84125E-3</v>
       </c>
       <c r="G281">
-        <v>-1.0729584558361389</v>
+        <v>-1.111001698746473</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.35">
@@ -8495,10 +8492,10 @@
         <v>0.88695151800000005</v>
       </c>
       <c r="F283">
-        <v>1.5063979956585101</v>
+        <v>1.5063979956585099E-2</v>
       </c>
       <c r="G283">
-        <v>-0.99999999999999867</v>
+        <v>-0.99999999999999822</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.35">
@@ -8521,7 +8518,7 @@
         <v>1.4380146999999999E-2</v>
       </c>
       <c r="G284">
-        <v>-0.96108208599352496</v>
+        <v>-0.99713388555450477</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.35">
@@ -8544,7 +8541,7 @@
         <v>4.8461679999999997E-3</v>
       </c>
       <c r="G285">
-        <v>-1.2083716055268701</v>
+        <v>-1.098142684242301</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.35">
@@ -8567,7 +8564,7 @@
         <v>2.0212369999999999E-3</v>
       </c>
       <c r="G286">
-        <v>-1.6238061915665529</v>
+        <v>-1.6910578467698021</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.35">
@@ -8590,7 +8587,7 @@
         <v>6.587079E-3</v>
       </c>
       <c r="G287">
-        <v>-1.1487125418389681</v>
+        <v>-1.166480251398659</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.35">
@@ -8610,7 +8607,7 @@
         <v>0.90284480600000006</v>
       </c>
       <c r="F288">
-        <v>5.6107026786420899</v>
+        <v>5.6107026786420898E-2</v>
       </c>
       <c r="G288">
         <v>-1</v>
@@ -8636,7 +8633,7 @@
         <v>9.6211608000000004E-2</v>
       </c>
       <c r="G289">
-        <v>-0.99999999999999889</v>
+        <v>-0.99999999999999944</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.35">
@@ -8659,7 +8656,7 @@
         <v>3.0942837000000001E-2</v>
       </c>
       <c r="G290">
-        <v>-0.7082580852456265</v>
+        <v>-0.72188783663165967</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.35">
@@ -8679,10 +8676,10 @@
         <v>-13.89534692</v>
       </c>
       <c r="F291">
-        <v>613.15423299891495</v>
+        <v>6.1315423299891494</v>
       </c>
       <c r="G291">
-        <v>-0.99999999999999889</v>
+        <v>-0.99999999999999967</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.35">
@@ -8751,7 +8748,7 @@
         <v>3.9102850000000003E-3</v>
       </c>
       <c r="G294">
-        <v>-1.216582614878607</v>
+        <v>-1.449562217076771</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.35">
@@ -8797,7 +8794,7 @@
         <v>2.5658337999999999E-2</v>
       </c>
       <c r="G296">
-        <v>-1.119619024711983</v>
+        <v>-1.161182800804442</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.35">
@@ -8820,7 +8817,7 @@
         <v>6.9085459999999998E-3</v>
       </c>
       <c r="G297">
-        <v>-1.317802081703455</v>
+        <v>-1.3437784649173861</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.35">
@@ -8851,22 +8848,22 @@
         <v>308</v>
       </c>
       <c r="B299" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C299">
-        <v>134.1033027</v>
+        <v>188.17773030000001</v>
       </c>
       <c r="D299">
-        <v>7.536186185</v>
+        <v>8.0138667560000005</v>
       </c>
       <c r="E299">
-        <v>0.80640469699999995</v>
+        <v>0.72834133199999995</v>
       </c>
       <c r="F299">
-        <v>1.292126213</v>
+        <v>1.0166123380000001</v>
       </c>
       <c r="G299">
-        <v>-1.4346964878937201</v>
+        <v>-0.45275968137334338</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.35">
@@ -8889,7 +8886,7 @@
         <v>1.3044722E-2</v>
       </c>
       <c r="G300">
-        <v>-0.98038328891060211</v>
+        <v>-0.99532114173705633</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.35">
@@ -8909,10 +8906,10 @@
         <v>-0.171322325</v>
       </c>
       <c r="F301">
-        <v>297.09951659415799</v>
+        <v>2.9709951659415799</v>
       </c>
       <c r="G301">
-        <v>-0.79999999999999793</v>
+        <v>-0.19999999999999629</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.35">
@@ -8935,7 +8932,7 @@
         <v>5.3824579999999997E-3</v>
       </c>
       <c r="G302">
-        <v>-1.0284827872446349</v>
+        <v>-1.0740734594818759</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.35">
@@ -8958,7 +8955,7 @@
         <v>4.1180829999999998E-3</v>
       </c>
       <c r="G303">
-        <v>-0.73734788023908504</v>
+        <v>-0.75217572329245275</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.35">
@@ -8981,7 +8978,7 @@
         <v>1.1241206E-2</v>
       </c>
       <c r="G304">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.35">
@@ -9004,7 +9001,7 @@
         <v>4.4894490000000004E-3</v>
       </c>
       <c r="G305">
-        <v>-0.81585509591780936</v>
+        <v>-0.8452993459050927</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.35">
@@ -9027,7 +9024,7 @@
         <v>0.137717178</v>
       </c>
       <c r="G306">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.35">
@@ -9050,7 +9047,7 @@
         <v>7.6153810000000001E-3</v>
       </c>
       <c r="G307">
-        <v>-1.040902022456045</v>
+        <v>-1.068578549068721</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.35">
@@ -9073,7 +9070,7 @@
         <v>8.5946779000000001E-2</v>
       </c>
       <c r="G308">
-        <v>2.4980018054066022E-16</v>
+        <v>-0.59999999999999942</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.35">
@@ -9096,7 +9093,7 @@
         <v>5.9612019999999996E-3</v>
       </c>
       <c r="G309">
-        <v>-1.1892925399890339</v>
+        <v>-1.280662132376347</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.35">
@@ -9119,7 +9116,7 @@
         <v>3.4512470000000002E-3</v>
       </c>
       <c r="G310">
-        <v>-1.59158330084751</v>
+        <v>-1.668662495835074</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.35">
@@ -9139,10 +9136,10 @@
         <v>0.40692237599999997</v>
       </c>
       <c r="F311">
-        <v>432.86298502124299</v>
+        <v>4.3286298502124296</v>
       </c>
       <c r="G311">
-        <v>-0.99999999999999978</v>
+        <v>-1.000000000000002</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.35">
@@ -9165,7 +9162,7 @@
         <v>1.7125702E-2</v>
       </c>
       <c r="G312">
-        <v>-0.9401145282631268</v>
+        <v>-0.94587567374264381</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.35">
@@ -9188,7 +9185,7 @@
         <v>3.8767451000000001E-2</v>
       </c>
       <c r="G313">
-        <v>-1.427298676134251</v>
+        <v>-1.499903206913044</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.35">
@@ -9211,7 +9208,7 @@
         <v>7.1855879999999997E-3</v>
       </c>
       <c r="G314">
-        <v>-1.006915899274101</v>
+        <v>-1.009943632522559</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.35">
@@ -9234,7 +9231,7 @@
         <v>6.1363620000000002E-3</v>
       </c>
       <c r="G315">
-        <v>-1.4104128295785601</v>
+        <v>-1.3991524951259671</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.35">
@@ -9257,7 +9254,7 @@
         <v>8.7753250000000005E-3</v>
       </c>
       <c r="G316">
-        <v>-0.2000000000000019</v>
+        <v>-0.20000000000000789</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.35">
@@ -9280,7 +9277,7 @@
         <v>9.4541899999999997E-4</v>
       </c>
       <c r="G317">
-        <v>-1.2152390630686249</v>
+        <v>-1.3003411400754621</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.35">
@@ -9303,7 +9300,7 @@
         <v>3.0541714000000001E-2</v>
       </c>
       <c r="G318">
-        <v>-0.99999999999999967</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.35">
@@ -9326,7 +9323,7 @@
         <v>1.0021545E-2</v>
       </c>
       <c r="G319">
-        <v>-1.5381592973853959</v>
+        <v>-1.5919717190885661</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.35">
@@ -9346,10 +9343,10 @@
         <v>0.98596461499999999</v>
       </c>
       <c r="F320">
-        <v>0.83227548134514195</v>
+        <v>8.322754813451419E-3</v>
       </c>
       <c r="G320">
-        <v>-0.82336530003708874</v>
+        <v>-1.065782729194503</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.35">
@@ -9372,7 +9369,7 @@
         <v>4.0042489999999997E-3</v>
       </c>
       <c r="G321">
-        <v>-1.166422808412648</v>
+        <v>-1.271546681425046</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.35">
@@ -9395,7 +9392,7 @@
         <v>1.7864841999999999E-2</v>
       </c>
       <c r="G322">
-        <v>-1.2170805777308491</v>
+        <v>-1.2466812164371559</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.35">
@@ -9418,7 +9415,7 @@
         <v>8.0585380000000005E-3</v>
       </c>
       <c r="G323">
-        <v>-0.96883303746600702</v>
+        <v>-0.98482236817015401</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.35">
@@ -9441,7 +9438,7 @@
         <v>0.101164165</v>
       </c>
       <c r="G324">
-        <v>-0.90491784147592891</v>
+        <v>-0.91076557808378122</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.35">
@@ -9464,7 +9461,7 @@
         <v>5.9516220000000002E-3</v>
       </c>
       <c r="G325">
-        <v>-1.557437463770095</v>
+        <v>-1.6527479080647789</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.35">
@@ -9487,7 +9484,7 @@
         <v>1.4774806999999999E-2</v>
       </c>
       <c r="G326">
-        <v>-1.0267480888055689</v>
+        <v>-1.035542340861012</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.35">
@@ -9507,10 +9504,10 @@
         <v>-3.4952981310000002</v>
       </c>
       <c r="F327">
-        <v>35.749957985365199</v>
+        <v>0.35749957985365199</v>
       </c>
       <c r="G327">
-        <v>-1</v>
+        <v>-0.99999999999999789</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.35">
@@ -9533,7 +9530,7 @@
         <v>1.645288E-2</v>
       </c>
       <c r="G328">
-        <v>-1.403683690269961</v>
+        <v>-1.4222616969773489</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.35">
@@ -9556,7 +9553,7 @@
         <v>1.3266599489999999</v>
       </c>
       <c r="G329">
-        <v>-0.81021181964202804</v>
+        <v>-0.80620414415937902</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.35">
@@ -9579,7 +9576,7 @@
         <v>5.2161259000000001E-2</v>
       </c>
       <c r="G330">
-        <v>-0.83965976633743411</v>
+        <v>-0.82163223934598539</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.35">
@@ -9599,10 +9596,10 @@
         <v>-12.06736021</v>
       </c>
       <c r="F331">
-        <v>47.957028513118203</v>
+        <v>0.47957028513118211</v>
       </c>
       <c r="G331">
-        <v>-0.99999999999999556</v>
+        <v>-0.99999999999999567</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.35">
@@ -9625,7 +9622,7 @@
         <v>2.1351915999999999E-2</v>
       </c>
       <c r="G332">
-        <v>-1.108938729691832</v>
+        <v>-1.1686996448614171</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.35">
@@ -9645,7 +9642,7 @@
         <v>0.97784954899999998</v>
       </c>
       <c r="F333">
-        <v>1.2468058229399499</v>
+        <v>1.24680582293995E-2</v>
       </c>
       <c r="G333">
         <v>-0.99999999999996059</v>
@@ -9717,7 +9714,7 @@
         <v>8.0131290000000008E-3</v>
       </c>
       <c r="G336">
-        <v>-0.9800358339062909</v>
+        <v>-1.0117427095077589</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.35">
@@ -9740,7 +9737,7 @@
         <v>3.1413090000000001E-3</v>
       </c>
       <c r="G337">
-        <v>-1.585182441694992</v>
+        <v>-1.670932935207706</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.35">
@@ -9763,7 +9760,7 @@
         <v>1.2092597E-2</v>
       </c>
       <c r="G338">
-        <v>-1.0220983623017439</v>
+        <v>-1.007436457352112</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.35">
@@ -9786,7 +9783,7 @@
         <v>3.8889229999999999E-3</v>
       </c>
       <c r="G339">
-        <v>-1.3417294823278481</v>
+        <v>-1.46600212516934</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.35">
@@ -9806,10 +9803,10 @@
         <v>0.95676154099999999</v>
       </c>
       <c r="F340">
-        <v>1.17215293429047</v>
+        <v>1.1721529342904701E-2</v>
       </c>
       <c r="G340">
-        <v>-0.99999999999999589</v>
+        <v>-0.99999999999999822</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.35">
@@ -9832,7 +9829,7 @@
         <v>2.5146056999999999E-2</v>
       </c>
       <c r="G341">
-        <v>-0.71725298385458225</v>
+        <v>-0.71867579110221902</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.35">
@@ -9855,7 +9852,7 @@
         <v>9.0569569999999992E-3</v>
       </c>
       <c r="G342">
-        <v>-1.550404314033285</v>
+        <v>-1.508638751927009</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.35">
@@ -9878,7 +9875,7 @@
         <v>4.2911709999999999E-3</v>
       </c>
       <c r="G343">
-        <v>-1.0187303494886419</v>
+        <v>-1.0887558680639791</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.35">
@@ -9898,10 +9895,10 @@
         <v>0.85011574499999998</v>
       </c>
       <c r="F344">
-        <v>3.4934634401981199</v>
+        <v>3.4934634401981197E-2</v>
       </c>
       <c r="G344">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999944</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.35">
@@ -9924,7 +9921,7 @@
         <v>6.0192450000000003E-3</v>
       </c>
       <c r="G345">
-        <v>-1.593200419545578</v>
+        <v>-1.6583286541628719</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.35">
@@ -9947,7 +9944,7 @@
         <v>3.1267887000000001E-2</v>
       </c>
       <c r="G346">
-        <v>-1.006913639475465</v>
+        <v>-1.028399869434631</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.35">
@@ -9970,7 +9967,7 @@
         <v>2.0893219999999998E-3</v>
       </c>
       <c r="G347">
-        <v>-0.75897882842941833</v>
+        <v>-0.79420119517672827</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.35">
@@ -9993,7 +9990,7 @@
         <v>5.5942509999999997E-3</v>
       </c>
       <c r="G348">
-        <v>-0.99999999999999967</v>
+        <v>-0.99999999999999933</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.35">
@@ -10016,7 +10013,7 @@
         <v>2.0563938E-2</v>
       </c>
       <c r="G349">
-        <v>-1.1964328887974569</v>
+        <v>-1.242302348279245</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.35">
@@ -10039,7 +10036,7 @@
         <v>5.0593011E-2</v>
       </c>
       <c r="G350">
-        <v>-0.99999999999999978</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.35">
@@ -10059,7 +10056,7 @@
         <v>0.99460705299999996</v>
       </c>
       <c r="F351">
-        <v>0.79375508748496104</v>
+        <v>7.937550874849611E-3</v>
       </c>
       <c r="G351">
         <v>-1.000000000000004</v>
@@ -10105,10 +10102,10 @@
         <v>-5.7550111000000001E-2</v>
       </c>
       <c r="F353">
-        <v>6.7609468684015699</v>
+        <v>6.7609468684015697E-2</v>
       </c>
       <c r="G353">
-        <v>-0.99999999999999956</v>
+        <v>-1.0000000000000011</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.35">
@@ -10131,7 +10128,7 @@
         <v>6.3238840000000001E-3</v>
       </c>
       <c r="G354">
-        <v>-0.50154181375074347</v>
+        <v>-0.51620487944231519</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.35">
@@ -10151,10 +10148,10 @@
         <v>0.80237370100000005</v>
       </c>
       <c r="F355">
-        <v>928.75735771775203</v>
+        <v>9.2875735771775201</v>
       </c>
       <c r="G355">
-        <v>-0.99999999999999956</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.35">
@@ -10177,7 +10174,7 @@
         <v>1.0737784239999999</v>
       </c>
       <c r="G356">
-        <v>-1.1563478307411419</v>
+        <v>-1.2668060666753189</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.35">
@@ -10223,7 +10220,7 @@
         <v>4.4462703999999999E-2</v>
       </c>
       <c r="G358">
-        <v>4.5935477643865852E-15</v>
+        <v>-0.59999999999999543</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.35">
@@ -10246,7 +10243,7 @@
         <v>5.0804270000000002E-3</v>
       </c>
       <c r="G359">
-        <v>-0.79096317409322903</v>
+        <v>-0.84203494629987941</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.35">
@@ -10269,7 +10266,7 @@
         <v>6.4897347999999994E-2</v>
       </c>
       <c r="G360">
-        <v>-1.1380668632220059</v>
+        <v>-1.2170923826660101</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.35">
@@ -10292,7 +10289,7 @@
         <v>8.3580990000000008E-3</v>
       </c>
       <c r="G361">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.35">
@@ -10315,7 +10312,7 @@
         <v>8.0433774999999999E-2</v>
       </c>
       <c r="G362">
-        <v>-1.061453141275627</v>
+        <v>-1.1283808951380201</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.35">
@@ -10338,7 +10335,7 @@
         <v>2.0295282000000001E-2</v>
       </c>
       <c r="G363">
-        <v>-1.1880281347979791</v>
+        <v>-1.236185980580049</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.35">
@@ -10361,7 +10358,7 @@
         <v>5.8081310000000002E-3</v>
       </c>
       <c r="G364">
-        <v>-1.023164933177388</v>
+        <v>-1.067382271660402</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.35">
@@ -10381,7 +10378,7 @@
         <v>-0.38108952200000001</v>
       </c>
       <c r="F365">
-        <v>6.5211169243354901</v>
+        <v>6.5211169243354905E-2</v>
       </c>
       <c r="G365">
         <v>-1</v>
@@ -10404,10 +10401,10 @@
         <v>-5.8910842079999997</v>
       </c>
       <c r="F366">
-        <v>179.15484167451999</v>
+        <v>1.7915484167452</v>
       </c>
       <c r="G366">
-        <v>-0.99999999999999878</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.35">
@@ -10427,10 +10424,10 @@
         <v>0.16123675800000001</v>
       </c>
       <c r="F367">
-        <v>1124.0665132510901</v>
+        <v>11.2406651325109</v>
       </c>
       <c r="G367">
-        <v>-0.2000000000000019</v>
+        <v>-0.19999999999999951</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.35">
@@ -10453,7 +10450,7 @@
         <v>2.5651209000000001E-2</v>
       </c>
       <c r="G368">
-        <v>-0.87300516590650168</v>
+        <v>-0.90414709723945352</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.35">
@@ -10476,7 +10473,7 @@
         <v>7.6856090000000004E-3</v>
       </c>
       <c r="G369">
-        <v>-0.81668506433764299</v>
+        <v>-0.82565385969094507</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.35">
@@ -10499,7 +10496,7 @@
         <v>1.1545138999999999E-2</v>
       </c>
       <c r="G370">
-        <v>-0.92489783664657266</v>
+        <v>-0.96317314545536825</v>
       </c>
     </row>
     <row r="371" spans="1:7" x14ac:dyDescent="0.35">
@@ -10522,7 +10519,7 @@
         <v>4.1469009999999997E-3</v>
       </c>
       <c r="G371">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999944</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.35">
@@ -10545,7 +10542,7 @@
         <v>4.2121989999999998E-3</v>
       </c>
       <c r="G372">
-        <v>-1.15897439224437</v>
+        <v>-1.3345203159817269</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.35">
@@ -10568,7 +10565,7 @@
         <v>8.9055599999999999E-3</v>
       </c>
       <c r="G373">
-        <v>-0.73641527966195253</v>
+        <v>-0.76011922440199986</v>
       </c>
     </row>
     <row r="374" spans="1:7" x14ac:dyDescent="0.35">
@@ -10591,7 +10588,7 @@
         <v>7.7236709999999997E-3</v>
       </c>
       <c r="G374">
-        <v>-0.98677248151390984</v>
+        <v>-1.0272154882500599</v>
       </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.35">
@@ -10611,10 +10608,10 @@
         <v>0.98830524200000003</v>
       </c>
       <c r="F375">
-        <v>2.11562956217898</v>
+        <v>2.1156295621789799E-2</v>
       </c>
       <c r="G375">
-        <v>-0.99999999999999722</v>
+        <v>-0.99999999999999922</v>
       </c>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.35">
@@ -10637,7 +10634,7 @@
         <v>6.4715709999999997E-3</v>
       </c>
       <c r="G376">
-        <v>-0.73830147454720285</v>
+        <v>-0.7705599515713546</v>
       </c>
     </row>
     <row r="377" spans="1:7" x14ac:dyDescent="0.35">
@@ -10660,7 +10657,7 @@
         <v>8.4541398000000004E-2</v>
       </c>
       <c r="G377">
-        <v>-0.32564095684672423</v>
+        <v>-1.0288207586847129</v>
       </c>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.35">
@@ -10683,7 +10680,7 @@
         <v>4.9412043000000003E-2</v>
       </c>
       <c r="G378">
-        <v>-1.0201672292111119</v>
+        <v>-1.021095816041123</v>
       </c>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.35">
@@ -10752,7 +10749,7 @@
         <v>1.0296227999999999E-2</v>
       </c>
       <c r="G381">
-        <v>-0.99999999999999845</v>
+        <v>-0.99999999999999811</v>
       </c>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.35">
@@ -10775,7 +10772,7 @@
         <v>5.3064430000000001E-3</v>
       </c>
       <c r="G382">
-        <v>-1.0030248742509309</v>
+        <v>-1.010351882118498</v>
       </c>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.35">
@@ -10795,10 +10792,10 @@
         <v>0.27692612799999999</v>
       </c>
       <c r="F383">
-        <v>4.2291213555304497</v>
+        <v>4.2291213555304498E-2</v>
       </c>
       <c r="G383">
-        <v>-0.99999999999999933</v>
+        <v>-0.99999999999999922</v>
       </c>
     </row>
     <row r="384" spans="1:7" x14ac:dyDescent="0.35">
@@ -10821,7 +10818,7 @@
         <v>2.7971609999999998E-3</v>
       </c>
       <c r="G384">
-        <v>-0.70969498972576539</v>
+        <v>-0.71342262193627315</v>
       </c>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.35">
@@ -10841,10 +10838,10 @@
         <v>0.73682318800000002</v>
       </c>
       <c r="F385">
-        <v>96.453945450996102</v>
+        <v>0.96453945450996104</v>
       </c>
       <c r="G385">
-        <v>-1.1521189477277241</v>
+        <v>-0.83515419649175471</v>
       </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.35">
@@ -10867,7 +10864,7 @@
         <v>5.6419740000000001E-3</v>
       </c>
       <c r="G386">
-        <v>-1.015088984178709</v>
+        <v>-1.0276937538183111</v>
       </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.35">
@@ -10890,7 +10887,7 @@
         <v>3.3559190000000002E-3</v>
       </c>
       <c r="G387">
-        <v>-0.75565603314726959</v>
+        <v>-0.78414101075183806</v>
       </c>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.35">
@@ -10913,7 +10910,7 @@
         <v>2.2238729999999999E-3</v>
       </c>
       <c r="G388">
-        <v>-1.429875146952071</v>
+        <v>-1.556711037150134</v>
       </c>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.35">
@@ -10936,7 +10933,7 @@
         <v>6.3820999999999999E-3</v>
       </c>
       <c r="G389">
-        <v>-0.78363316092351176</v>
+        <v>-0.90381459432936961</v>
       </c>
     </row>
     <row r="390" spans="1:7" x14ac:dyDescent="0.35">
@@ -10959,7 +10956,7 @@
         <v>2.1525239999999998E-3</v>
       </c>
       <c r="G390">
-        <v>-0.99999999999999545</v>
+        <v>-0.99999999999999556</v>
       </c>
     </row>
     <row r="391" spans="1:7" x14ac:dyDescent="0.35">
@@ -10982,7 +10979,7 @@
         <v>4.5978169999999997E-3</v>
       </c>
       <c r="G391">
-        <v>-1.2945929457440739</v>
+        <v>-1.4047619224844961</v>
       </c>
     </row>
     <row r="392" spans="1:7" x14ac:dyDescent="0.35">
@@ -11005,7 +11002,7 @@
         <v>4.6417369999999999E-3</v>
       </c>
       <c r="G392">
-        <v>-1.3536444303135939</v>
+        <v>-1.384971225644267</v>
       </c>
     </row>
     <row r="393" spans="1:7" x14ac:dyDescent="0.35">
@@ -11025,10 +11022,10 @@
         <v>0.78224735999999995</v>
       </c>
       <c r="F393">
-        <v>6.1990650197576898</v>
+        <v>6.1990650197576901E-2</v>
       </c>
       <c r="G393">
-        <v>-0.79999999999999061</v>
+        <v>-0.20000000000001311</v>
       </c>
     </row>
     <row r="394" spans="1:7" x14ac:dyDescent="0.35">
@@ -11071,10 +11068,10 @@
         <v>0.96922694200000004</v>
       </c>
       <c r="F395">
-        <v>0.70166316478993096</v>
+        <v>7.0166316478993086E-3</v>
       </c>
       <c r="G395">
-        <v>0</v>
+        <v>-0.59999999999999809</v>
       </c>
     </row>
     <row r="396" spans="1:7" x14ac:dyDescent="0.35">
@@ -11082,22 +11079,22 @@
         <v>405</v>
       </c>
       <c r="B396" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C396">
-        <v>12411.597449999999</v>
+        <v>37107.977460000002</v>
       </c>
       <c r="D396">
-        <v>92.947240460000003</v>
+        <v>97.915450440000001</v>
       </c>
       <c r="E396">
-        <v>-2.055470063</v>
+        <v>0.71170724900000004</v>
       </c>
       <c r="F396">
-        <v>13.238264781556399</v>
+        <v>6.6749458999999997E-2</v>
       </c>
       <c r="G396">
-        <v>-0.82081594627509835</v>
+        <v>-0.27247026623185072</v>
       </c>
     </row>
     <row r="397" spans="1:7" x14ac:dyDescent="0.35">
@@ -11117,10 +11114,10 @@
         <v>0.90090940500000005</v>
       </c>
       <c r="F397">
-        <v>5.8429342363232504</v>
+        <v>5.8429342363232502E-2</v>
       </c>
       <c r="G397">
-        <v>-0.63028111234976936</v>
+        <v>-0.35860425742776209</v>
       </c>
     </row>
     <row r="398" spans="1:7" x14ac:dyDescent="0.35">
@@ -11143,7 +11140,7 @@
         <v>3.158213E-3</v>
       </c>
       <c r="G398">
-        <v>-1.241833087993101</v>
+        <v>-1.329915377584709</v>
       </c>
     </row>
     <row r="399" spans="1:7" x14ac:dyDescent="0.35">
@@ -11163,10 +11160,10 @@
         <v>-2.8505253179999999</v>
       </c>
       <c r="F399">
-        <v>87.008959904318004</v>
+        <v>0.87008959904318006</v>
       </c>
       <c r="G399">
-        <v>-0.8000000000000026</v>
+        <v>-0.199999999999982</v>
       </c>
     </row>
     <row r="400" spans="1:7" x14ac:dyDescent="0.35">
@@ -11186,7 +11183,7 @@
         <v>0.45446371099999999</v>
       </c>
       <c r="F400">
-        <v>17.096639067722101</v>
+        <v>0.170966390677221</v>
       </c>
       <c r="G400">
         <v>-1</v>
@@ -11212,7 +11209,7 @@
         <v>3.292424E-2</v>
       </c>
       <c r="G401">
-        <v>-0.88088526337063544</v>
+        <v>-0.90308346952757634</v>
       </c>
     </row>
     <row r="402" spans="1:7" x14ac:dyDescent="0.35">
@@ -11235,7 +11232,7 @@
         <v>1.7667873000000001E-2</v>
       </c>
       <c r="G402">
-        <v>-1.079288542557614</v>
+        <v>-1.133895105503971</v>
       </c>
     </row>
     <row r="403" spans="1:7" x14ac:dyDescent="0.35">
@@ -11281,7 +11278,7 @@
         <v>5.6162139999999996E-3</v>
       </c>
       <c r="G404">
-        <v>-0.80181171437193843</v>
+        <v>-0.92440933103543887</v>
       </c>
     </row>
     <row r="405" spans="1:7" x14ac:dyDescent="0.35">
@@ -11304,7 +11301,7 @@
         <v>6.7536030000000004E-3</v>
       </c>
       <c r="G405">
-        <v>-0.74243679854283107</v>
+        <v>-0.81535057337731165</v>
       </c>
     </row>
     <row r="406" spans="1:7" x14ac:dyDescent="0.35">
@@ -11327,7 +11324,7 @@
         <v>5.7782129999999999E-3</v>
       </c>
       <c r="G406">
-        <v>-0.99999999999999756</v>
+        <v>-0.99999999999999745</v>
       </c>
     </row>
     <row r="407" spans="1:7" x14ac:dyDescent="0.35">
@@ -11350,7 +11347,7 @@
         <v>8.3234137E-2</v>
       </c>
       <c r="G407">
-        <v>-0.99190641079781616</v>
+        <v>-1.00262198186937</v>
       </c>
     </row>
     <row r="408" spans="1:7" x14ac:dyDescent="0.35">
@@ -11370,7 +11367,7 @@
         <v>0.91896202999999999</v>
       </c>
       <c r="F408">
-        <v>1.86729227446501</v>
+        <v>1.86729227446501E-2</v>
       </c>
       <c r="G408">
         <v>-1</v>
@@ -11396,7 +11393,7 @@
         <v>4.2589230000000004E-3</v>
       </c>
       <c r="G409">
-        <v>-1.481737001794925</v>
+        <v>-1.5755742292690009</v>
       </c>
     </row>
     <row r="410" spans="1:7" x14ac:dyDescent="0.35">
@@ -11419,7 +11416,7 @@
         <v>1.5392288E-2</v>
       </c>
       <c r="G410">
-        <v>-0.56737755195368877</v>
+        <v>-0.5940532219327237</v>
       </c>
     </row>
     <row r="411" spans="1:7" x14ac:dyDescent="0.35">
@@ -11442,7 +11439,7 @@
         <v>2.7838659999999999E-3</v>
       </c>
       <c r="G411">
-        <v>-1.250956575914119</v>
+        <v>-1.3711178390646721</v>
       </c>
     </row>
     <row r="412" spans="1:7" x14ac:dyDescent="0.35">
@@ -11462,10 +11459,10 @@
         <v>0.96439451200000004</v>
       </c>
       <c r="F412">
-        <v>1.12449828968024</v>
+        <v>1.12449828968024E-2</v>
       </c>
       <c r="G412">
-        <v>-0.96290977245457976</v>
+        <v>-0.87962163549257333</v>
       </c>
     </row>
     <row r="413" spans="1:7" x14ac:dyDescent="0.35">
@@ -11488,7 +11485,7 @@
         <v>1.0168652E-2</v>
       </c>
       <c r="G413">
-        <v>-1.26864219918515</v>
+        <v>-1.373383015808092</v>
       </c>
     </row>
     <row r="414" spans="1:7" x14ac:dyDescent="0.35">
@@ -11534,7 +11531,7 @@
         <v>6.9193680000000004E-3</v>
       </c>
       <c r="G415">
-        <v>-0.85304822676385628</v>
+        <v>-0.86517959765553443</v>
       </c>
     </row>
     <row r="416" spans="1:7" x14ac:dyDescent="0.35">
@@ -11557,7 +11554,7 @@
         <v>3.0981260000000001E-3</v>
       </c>
       <c r="G416">
-        <v>-1.4493663343531169</v>
+        <v>-1.4714375638612049</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.35">
@@ -11580,7 +11577,7 @@
         <v>6.6039779999999999E-3</v>
       </c>
       <c r="G417">
-        <v>-1.060591427770136</v>
+        <v>-1.082130593847106</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.35">
@@ -11603,7 +11600,7 @@
         <v>4.6033159999999997E-3</v>
       </c>
       <c r="G418">
-        <v>-1.5360755004421309</v>
+        <v>-1.6131062401152221</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.35">
@@ -11626,7 +11623,7 @@
         <v>5.4054810000000002E-3</v>
       </c>
       <c r="G419">
-        <v>-1.3618006680440911</v>
+        <v>-1.4374530992335921</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.35">
@@ -11634,22 +11631,22 @@
         <v>429</v>
       </c>
       <c r="B420" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C420">
-        <v>0.73395667499999995</v>
+        <v>674.26758859999995</v>
       </c>
       <c r="D420">
-        <v>0.41050614800000002</v>
+        <v>15.834627319999999</v>
       </c>
       <c r="E420">
-        <v>-0.29802434799999999</v>
+        <v>0.97328339900000005</v>
       </c>
       <c r="F420">
-        <v>7.6243160802080503</v>
+        <v>2.4980925000000001E-2</v>
       </c>
       <c r="G420">
-        <v>-0.49869842430392508</v>
+        <v>-0.46601638938666551</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.35">
@@ -11672,7 +11669,7 @@
         <v>8.5568453410000007</v>
       </c>
       <c r="G421">
-        <v>-1.004559045026181</v>
+        <v>-0.26119561922455092</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.35">
@@ -11692,10 +11689,10 @@
         <v>-0.26376280699999999</v>
       </c>
       <c r="F422">
-        <v>14.8658733588403</v>
+        <v>0.14865873358840301</v>
       </c>
       <c r="G422">
-        <v>-0.99999999999999956</v>
+        <v>-0.99999999999999933</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.35">
@@ -11718,7 +11715,7 @@
         <v>5.2351089999999999E-3</v>
       </c>
       <c r="G423">
-        <v>-0.89108351900560645</v>
+        <v>-0.90735855044811875</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.35">
@@ -11738,10 +11735,10 @@
         <v>0.92649563099999999</v>
       </c>
       <c r="F424">
-        <v>1.0399281807579701</v>
+        <v>1.0399281807579701E-2</v>
       </c>
       <c r="G424">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999956</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.35">
@@ -11764,7 +11761,7 @@
         <v>7.2709380000000002E-3</v>
       </c>
       <c r="G425">
-        <v>-0.71834558835415319</v>
+        <v>-0.72883683411034228</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.35">
@@ -11810,7 +11807,7 @@
         <v>9.1516800000000006E-3</v>
       </c>
       <c r="G427">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999956</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.35">
@@ -11833,7 +11830,7 @@
         <v>2.0453099999999998E-3</v>
       </c>
       <c r="G428">
-        <v>-1.049773415822147</v>
+        <v>-1.079354282603624</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.35">
@@ -11853,10 +11850,10 @@
         <v>-6.569407515</v>
       </c>
       <c r="F429">
-        <v>110.192093731355</v>
+        <v>1.1019209373135499</v>
       </c>
       <c r="G429">
-        <v>-0.76381217554992675</v>
+        <v>-0.36439960972749741</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.35">
@@ -11876,7 +11873,7 @@
         <v>0.54487480399999999</v>
       </c>
       <c r="F430">
-        <v>3.9331135979965302</v>
+        <v>3.93311359799653E-2</v>
       </c>
       <c r="G430">
         <v>-0.99999999999999978</v>
@@ -11902,7 +11899,7 @@
         <v>3.3891120000000001E-3</v>
       </c>
       <c r="G431">
-        <v>-1.0542764403626981</v>
+        <v>-1.0882078720884409</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.35">
@@ -11925,7 +11922,7 @@
         <v>4.4477579999999996E-3</v>
       </c>
       <c r="G432">
-        <v>-0.78685136537312084</v>
+        <v>-0.8754345588185517</v>
       </c>
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.35">
@@ -11948,7 +11945,7 @@
         <v>1.4276199999999999E-2</v>
       </c>
       <c r="G433">
-        <v>-1.1245125668949421</v>
+        <v>-1.1900769945071039</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.35">
@@ -11968,10 +11965,10 @@
         <v>5.5730646000000002E-2</v>
       </c>
       <c r="F434">
-        <v>1006.52867578375</v>
+        <v>10.0652867578375</v>
       </c>
       <c r="G434">
-        <v>-1</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.35">
@@ -11994,7 +11991,7 @@
         <v>7.2201080000000003E-3</v>
       </c>
       <c r="G435">
-        <v>-0.97879486418650963</v>
+        <v>-1.1968893935538281</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.35">
@@ -12040,7 +12037,7 @@
         <v>0.13793915400000001</v>
       </c>
       <c r="G437">
-        <v>-1.0512246454658101</v>
+        <v>-1.068608179032333</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.35">
@@ -12048,22 +12045,22 @@
         <v>447</v>
       </c>
       <c r="B438" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C438">
-        <v>46.719770769999997</v>
+        <v>73157.399749999997</v>
       </c>
       <c r="D438">
-        <v>6.4390404639999996</v>
+        <v>170.5328097</v>
       </c>
       <c r="E438">
-        <v>-9.3457193669999992</v>
+        <v>0.86177151100000005</v>
       </c>
       <c r="F438">
-        <v>15.6070669456521</v>
+        <v>3.1310691000000002E-2</v>
       </c>
       <c r="G438">
-        <v>-0.38184470129420939</v>
+        <v>-0.37181622993593372</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.35">
@@ -12086,7 +12083,7 @@
         <v>0.23112877600000001</v>
       </c>
       <c r="G439">
-        <v>-1.738031007399274</v>
+        <v>-1.9157127102113869</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.35">
@@ -12109,7 +12106,7 @@
         <v>1.3121282999999999E-2</v>
       </c>
       <c r="G440">
-        <v>-1.0045714564490871</v>
+        <v>-1.005240099743606</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.35">
@@ -12132,7 +12129,7 @@
         <v>2.5303334E-2</v>
       </c>
       <c r="G441">
-        <v>-1.005283180980808</v>
+        <v>-1.0051727686564811</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.35">
@@ -12152,10 +12149,10 @@
         <v>-16.652861439999999</v>
       </c>
       <c r="F442">
-        <v>989.077177942611</v>
+        <v>9.8907717794261103</v>
       </c>
       <c r="G442">
-        <v>-0.20000000000000079</v>
+        <v>-0.2000000000000004</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.35">
@@ -12178,7 +12175,7 @@
         <v>0.11259437899999999</v>
       </c>
       <c r="G443">
-        <v>-0.92604566405843347</v>
+        <v>-0.96765989721549661</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.35">
@@ -12201,7 +12198,7 @@
         <v>9.9787417000000003E-2</v>
       </c>
       <c r="G444">
-        <v>-0.79544620054389836</v>
+        <v>-0.79706333262657048</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.35">
@@ -12224,7 +12221,7 @@
         <v>2.3539820000000001E-3</v>
       </c>
       <c r="G445">
-        <v>-1.10211792652594</v>
+        <v>-1.1279641136444161</v>
       </c>
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.35">
@@ -12270,7 +12267,7 @@
         <v>1.1521247E-2</v>
       </c>
       <c r="G447">
-        <v>-1.1711646990147291</v>
+        <v>-1.3105244586315841</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.35">
@@ -12278,22 +12275,22 @@
         <v>457</v>
       </c>
       <c r="B448" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C448">
-        <v>27400.718280000001</v>
+        <v>27422.298070000001</v>
       </c>
       <c r="D448">
-        <v>97.994738900000002</v>
+        <v>96.930314620000004</v>
       </c>
       <c r="E448">
-        <v>0.52546025600000001</v>
+        <v>0.52508652700000003</v>
       </c>
       <c r="F448">
-        <v>82.679802165460003</v>
+        <v>0.82145952882845097</v>
       </c>
       <c r="G448">
-        <v>-3.767819389821625E-14</v>
+        <v>-0.60000000000000375</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.35">
@@ -12316,7 +12313,7 @@
         <v>2.0193801000000001E-2</v>
       </c>
       <c r="G449">
-        <v>-1.0000000000000011</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.35">
@@ -12339,7 +12336,7 @@
         <v>1.3365121000000001E-2</v>
       </c>
       <c r="G450">
-        <v>-1.066070686449673</v>
+        <v>-1.0862224573307759</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.35">
@@ -12362,7 +12359,7 @@
         <v>7.943337E-3</v>
       </c>
       <c r="G451">
-        <v>-0.99999999999999778</v>
+        <v>-0.999999999999998</v>
       </c>
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.35">
@@ -12385,7 +12382,7 @@
         <v>2.4432537000000001E-2</v>
       </c>
       <c r="G452">
-        <v>-1.0279980734560721</v>
+        <v>-1.099289020779213</v>
       </c>
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.35">
@@ -12408,7 +12405,7 @@
         <v>9.6982779999999994E-3</v>
       </c>
       <c r="G453">
-        <v>-0.71419464380228614</v>
+        <v>-0.78531017807818082</v>
       </c>
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.35">
@@ -12428,7 +12425,7 @@
         <v>0.91368646799999997</v>
       </c>
       <c r="F454">
-        <v>2.2166408845429499</v>
+        <v>2.2166408845429499E-2</v>
       </c>
       <c r="G454">
         <v>-1</v>
@@ -12454,7 +12451,7 @@
         <v>1.0104253000000001E-2</v>
       </c>
       <c r="G455">
-        <v>-0.99999999999999978</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.35">
@@ -12477,7 +12474,7 @@
         <v>3.7063532000000003E-2</v>
       </c>
       <c r="G456">
-        <v>-0.96608854933416277</v>
+        <v>-0.99037802778356065</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.35">
@@ -12500,7 +12497,7 @@
         <v>3.9994219999999999E-3</v>
       </c>
       <c r="G457">
-        <v>-0.99999999999999933</v>
+        <v>-0.99999999999999956</v>
       </c>
     </row>
     <row r="458" spans="1:7" x14ac:dyDescent="0.35">
@@ -12520,7 +12517,7 @@
         <v>0.92679129699999996</v>
       </c>
       <c r="F458">
-        <v>1.73818344050431</v>
+        <v>1.7381834405043099E-2</v>
       </c>
       <c r="G458">
         <v>-1</v>
@@ -12546,7 +12543,7 @@
         <v>2.2496449000000002E-2</v>
       </c>
       <c r="G459">
-        <v>-1.056976064206804</v>
+        <v>-1.069295549614186</v>
       </c>
     </row>
     <row r="460" spans="1:7" x14ac:dyDescent="0.35">
@@ -12569,7 +12566,7 @@
         <v>7.8298269999999993E-3</v>
       </c>
       <c r="G460">
-        <v>-0.95472845731805722</v>
+        <v>-1.052351837035485</v>
       </c>
     </row>
     <row r="461" spans="1:7" x14ac:dyDescent="0.35">
@@ -12592,7 +12589,7 @@
         <v>9.9762779999999999E-3</v>
       </c>
       <c r="G461">
-        <v>-1.301899063676669</v>
+        <v>-1.297179143443435</v>
       </c>
     </row>
     <row r="462" spans="1:7" x14ac:dyDescent="0.35">
@@ -12615,7 +12612,7 @@
         <v>2.0582484000000002E-2</v>
       </c>
       <c r="G462">
-        <v>-1.054697726542819</v>
+        <v>-1.071386502673642</v>
       </c>
     </row>
     <row r="463" spans="1:7" x14ac:dyDescent="0.35">
@@ -12638,7 +12635,7 @@
         <v>5.6817380000000004E-3</v>
       </c>
       <c r="G463">
-        <v>-1.396085496630453</v>
+        <v>-1.441615088298414</v>
       </c>
     </row>
     <row r="464" spans="1:7" x14ac:dyDescent="0.35">
@@ -12661,7 +12658,7 @@
         <v>3.1121559E-2</v>
       </c>
       <c r="G464">
-        <v>-1.01878604035858</v>
+        <v>-1.032673869889462</v>
       </c>
     </row>
     <row r="465" spans="1:7" x14ac:dyDescent="0.35">
@@ -12684,7 +12681,7 @@
         <v>2.6831774999999999E-2</v>
       </c>
       <c r="G465">
-        <v>-0.65513895571844483</v>
+        <v>-0.66462349537007903</v>
       </c>
     </row>
     <row r="466" spans="1:7" x14ac:dyDescent="0.35">
@@ -12704,7 +12701,7 @@
         <v>0.96692478000000004</v>
       </c>
       <c r="F466">
-        <v>1.03966440760715</v>
+        <v>1.03966440760715E-2</v>
       </c>
       <c r="G466">
         <v>-1</v>
@@ -12753,7 +12750,7 @@
         <v>1.7125772000000001E-2</v>
       </c>
       <c r="G468">
-        <v>-0.70348340960657041</v>
+        <v>-0.73485927551032471</v>
       </c>
     </row>
     <row r="469" spans="1:7" x14ac:dyDescent="0.35">
@@ -12776,7 +12773,7 @@
         <v>1.7338698999999999E-2</v>
       </c>
       <c r="G469">
-        <v>-1.086254647455696</v>
+        <v>-1.1111528840138709</v>
       </c>
     </row>
     <row r="470" spans="1:7" x14ac:dyDescent="0.35">
@@ -12799,7 +12796,7 @@
         <v>4.1334190000000002E-3</v>
       </c>
       <c r="G470">
-        <v>-1.0000000000000011</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="471" spans="1:7" x14ac:dyDescent="0.35">
@@ -12830,22 +12827,22 @@
         <v>481</v>
       </c>
       <c r="B472" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C472">
-        <v>1.056898039</v>
+        <v>1.078474916</v>
       </c>
       <c r="D472">
-        <v>0.80414629599999998</v>
+        <v>0.76800958100000005</v>
       </c>
       <c r="E472">
-        <v>0.94368996199999999</v>
+        <v>0.94254037599999996</v>
       </c>
       <c r="F472">
-        <v>2.1699947866302902</v>
+        <v>2.0799143002162498E-2</v>
       </c>
       <c r="G472">
-        <v>-1.498801083243961E-14</v>
+        <v>-0.60000000000001197</v>
       </c>
     </row>
     <row r="473" spans="1:7" x14ac:dyDescent="0.35">
@@ -12888,7 +12885,7 @@
         <v>-70.368646769999998</v>
       </c>
       <c r="F474">
-        <v>240.24570517992399</v>
+        <v>2.4024570517992401</v>
       </c>
       <c r="G474">
         <v>-1</v>
@@ -12914,7 +12911,7 @@
         <v>1.128531E-2</v>
       </c>
       <c r="G475">
-        <v>-0.71502269630525739</v>
+        <v>-0.72317807147256274</v>
       </c>
     </row>
     <row r="476" spans="1:7" x14ac:dyDescent="0.35">
@@ -12934,10 +12931,10 @@
         <v>0.38861582500000003</v>
       </c>
       <c r="F476">
-        <v>821.23825599257702</v>
+        <v>8.2123825599257696</v>
       </c>
       <c r="G476">
-        <v>-0.999999999999999</v>
+        <v>-0.99999999999999911</v>
       </c>
     </row>
     <row r="477" spans="1:7" x14ac:dyDescent="0.35">
@@ -12957,7 +12954,7 @@
         <v>-4.2853304850000002</v>
       </c>
       <c r="F477">
-        <v>250.80061003445499</v>
+        <v>2.50800610034455</v>
       </c>
       <c r="G477">
         <v>-1</v>
@@ -12983,7 +12980,7 @@
         <v>8.3736220000000007E-3</v>
       </c>
       <c r="G478">
-        <v>-0.75725334153177182</v>
+        <v>-0.79364530795518051</v>
       </c>
     </row>
     <row r="479" spans="1:7" x14ac:dyDescent="0.35">
@@ -13006,7 +13003,7 @@
         <v>8.6519630000000004E-3</v>
       </c>
       <c r="G479">
-        <v>-0.77804556244669532</v>
+        <v>-0.81394524496238296</v>
       </c>
     </row>
     <row r="480" spans="1:7" x14ac:dyDescent="0.35">
@@ -13029,7 +13026,7 @@
         <v>4.4076760000000001E-3</v>
       </c>
       <c r="G480">
-        <v>-0.99999999999999845</v>
+        <v>-0.99999999999999944</v>
       </c>
     </row>
     <row r="481" spans="1:7" x14ac:dyDescent="0.35">
@@ -13052,7 +13049,7 @@
         <v>0.47442943100000001</v>
       </c>
       <c r="G481">
-        <v>-1.00707603550682</v>
+        <v>-1.007439726418073</v>
       </c>
     </row>
     <row r="482" spans="1:7" x14ac:dyDescent="0.35">
@@ -13075,7 +13072,7 @@
         <v>1.0531522999999999E-2</v>
       </c>
       <c r="G482">
-        <v>-1.3336528977622979</v>
+        <v>-1.491065082502824</v>
       </c>
     </row>
     <row r="483" spans="1:7" x14ac:dyDescent="0.35">
@@ -13098,7 +13095,7 @@
         <v>3.1676600000000001E-3</v>
       </c>
       <c r="G483">
-        <v>-1.066521864480025</v>
+        <v>-1.194224532299726</v>
       </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.35">
@@ -13118,10 +13115,10 @@
         <v>-0.62337098199999996</v>
       </c>
       <c r="F484">
-        <v>60.713470773354501</v>
+        <v>0.60713470773354505</v>
       </c>
       <c r="G484">
-        <v>-0.99999999999999989</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.35">
@@ -13144,7 +13141,7 @@
         <v>1.364888E-2</v>
       </c>
       <c r="G485">
-        <v>-1</v>
+        <v>-0.99999999999999989</v>
       </c>
     </row>
     <row r="486" spans="1:7" x14ac:dyDescent="0.35">
@@ -13152,22 +13149,22 @@
         <v>495</v>
       </c>
       <c r="B486" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C486">
-        <v>1.5238599370000001</v>
+        <v>2051.302396</v>
       </c>
       <c r="D486">
-        <v>1.0229564120000001</v>
+        <v>30.613726539999998</v>
       </c>
       <c r="E486">
-        <v>0.96262417</v>
+        <v>0.99619361900000003</v>
       </c>
       <c r="F486">
-        <v>2.6628462801075199</v>
+        <v>5.7762309999999997E-3</v>
       </c>
       <c r="G486">
-        <v>-0.5370898058150001</v>
+        <v>-0.52115199576956495</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.35">
@@ -13233,7 +13230,7 @@
         <v>0.96809332699999995</v>
       </c>
       <c r="F489">
-        <v>3.1556584307776601</v>
+        <v>3.1556584307776601E-2</v>
       </c>
       <c r="G489">
         <v>-1</v>
@@ -13244,22 +13241,22 @@
         <v>499</v>
       </c>
       <c r="B490" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C490">
-        <v>6.9400000000000006E-5</v>
+        <v>3.1297818999999998E-2</v>
       </c>
       <c r="D490">
-        <v>6.4697110000000004E-3</v>
+        <v>9.2227744E-2</v>
       </c>
       <c r="E490">
-        <v>0.90192950900000002</v>
+        <v>0.980793315</v>
       </c>
       <c r="F490">
-        <v>7.5925649300357598</v>
+        <v>1.4520866E-2</v>
       </c>
       <c r="G490">
-        <v>-0.37445542970982632</v>
+        <v>-0.75565123083066765</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.35">
@@ -13279,7 +13276,7 @@
         <v>0.94890533600000004</v>
       </c>
       <c r="F491">
-        <v>1.6160620750171699</v>
+        <v>1.61606207501717E-2</v>
       </c>
       <c r="G491">
         <v>-1.0000000000000031</v>
@@ -13302,10 +13299,10 @@
         <v>0.96932228300000001</v>
       </c>
       <c r="F492">
-        <v>1.52370871308726</v>
+        <v>1.5237087130872601E-2</v>
       </c>
       <c r="G492">
-        <v>-1.0544328241064751</v>
+        <v>-0.95328491245383695</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.35">
@@ -13325,7 +13322,7 @@
         <v>0.53715178900000005</v>
       </c>
       <c r="F493">
-        <v>330.09018944634602</v>
+        <v>3.3009018944634598</v>
       </c>
       <c r="G493">
         <v>-1</v>
@@ -13351,7 +13348,7 @@
         <v>2.8810179999999999E-3</v>
       </c>
       <c r="G494">
-        <v>-0.74395216318398538</v>
+        <v>-0.7599584690982526</v>
       </c>
     </row>
     <row r="495" spans="1:7" x14ac:dyDescent="0.35">
@@ -13374,7 +13371,7 @@
         <v>1.0114306E-2</v>
       </c>
       <c r="G495">
-        <v>-0.60185453346271633</v>
+        <v>-0.98579803292485735</v>
       </c>
     </row>
     <row r="496" spans="1:7" x14ac:dyDescent="0.35">
